--- a/content/oeuvres.xlsx
+++ b/content/oeuvres.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\web\henassa-archives\content\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02DE4A65-0599-402F-8518-7813DBE11C4A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAFB8F5-1242-48EE-9838-1F235E02D0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11535" uniqueCount="7581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12417" uniqueCount="7994">
   <si>
     <t>id</t>
   </si>
@@ -22765,6 +22765,1245 @@
   </si>
   <si>
     <t>Tedax Max (guest), Boucherie Chevaline guest6 (guest), Loveni (guest)</t>
+  </si>
+  <si>
+    <t>stromae-cheese</t>
+  </si>
+  <si>
+    <t>Cheese</t>
+  </si>
+  <si>
+    <t>Stromae</t>
+  </si>
+  <si>
+    <t>Electropop, Electro House, Electro Hop, Dance-Pop</t>
+  </si>
+  <si>
+    <t>Hip Hop, Nouvelle chanson française, Hip House</t>
+  </si>
+  <si>
+    <t>male vocalist, sombre, introspective, urban, party, energetic, rhythmic, sarcastic, summer</t>
+  </si>
+  <si>
+    <t>2010-06-17</t>
+  </si>
+  <si>
+    <t>Mosaert, Universal International, Mercury, Vertigo</t>
+  </si>
+  <si>
+    <t>Mosaert producer</t>
+  </si>
+  <si>
+    <t>Bionix (consultant)</t>
+  </si>
+  <si>
+    <t>Pieter Wagter (mastering), Lion Hell Capouillez mixing (mixage)</t>
+  </si>
+  <si>
+    <t>Luc Junior Tam art direction (art direction), Romain Bilharz (art direction), Dati Bendo graphic design (graphic design, photography), Guillaume Mortier graphic design (graphic design)</t>
+  </si>
+  <si>
+    <t>38:57</t>
+  </si>
+  <si>
+    <t>pnl-dans-la-legende</t>
+  </si>
+  <si>
+    <t>Dans la légende</t>
+  </si>
+  <si>
+    <t>ethereal, drugs, urban, angry, melancholic, money, male vocalist, atmospheric, bittersweet, melodic, rhythmic, hypnotic, regret, family, alienation, community, boastful, Islamic, crime</t>
+  </si>
+  <si>
+    <t>2016-09-16</t>
+  </si>
+  <si>
+    <t>75:46</t>
+  </si>
+  <si>
+    <t>orelsan-la-fete-est-finie</t>
+  </si>
+  <si>
+    <t>La fête est finie</t>
+  </si>
+  <si>
+    <t>Orelsan</t>
+  </si>
+  <si>
+    <t>male vocalist, bittersweet, longing, melancholic, humorous, urban, conscious, autumn, pessimistic, nostalgia, family, sarcastic, atmospheric, love, self-hatred, introspective, vulgar</t>
+  </si>
+  <si>
+    <t>2017-10-20</t>
+  </si>
+  <si>
+    <t>7th Magnitude, 3ème Bureau</t>
+  </si>
+  <si>
+    <t>GIMS, Nekfeu, Dizzee Rascal, Stromae, Ibeyi</t>
+  </si>
+  <si>
+    <t>50:03</t>
+  </si>
+  <si>
+    <t>orelsan-le-chant-des-sirenes</t>
+  </si>
+  <si>
+    <t>Le chant des sirènes</t>
+  </si>
+  <si>
+    <t>Pop Rap, Hardcore Hip Hop, Conscious Hip Hop, Brostep</t>
+  </si>
+  <si>
+    <t>pessimistic, political, anxious, hateful, urban, death, introspective, self-hatred, fame, male vocalist, technology, futuristic, ominous, lonely, sexual, nihilistic, sarcastic</t>
+  </si>
+  <si>
+    <t>2011-09-26</t>
+  </si>
+  <si>
+    <t>3ème Bureau</t>
+  </si>
+  <si>
+    <t>Gringe</t>
+  </si>
+  <si>
+    <t>62:54</t>
+  </si>
+  <si>
+    <t>vald-ce-monde-est-cruel</t>
+  </si>
+  <si>
+    <t>Ce monde est cruel</t>
+  </si>
+  <si>
+    <t>vulgar, political, anxious, dark, aggressive, conscious, depressive, lonely, rhythmic, cynical, alienation, sarcastic, boastful, male vocalist, serious</t>
+  </si>
+  <si>
+    <t>2019-10-11</t>
+  </si>
+  <si>
+    <t>Suik'on Blaze AD, SCH, Maes</t>
+  </si>
+  <si>
+    <t>56:23</t>
+  </si>
+  <si>
+    <t>nekfeu-feu</t>
+  </si>
+  <si>
+    <t>Feu</t>
+  </si>
+  <si>
+    <t>Nekfeu</t>
+  </si>
+  <si>
+    <t>conscious, introspective, urban, sentimental, male vocalist, melancholic, atmospheric, love, passionate</t>
+  </si>
+  <si>
+    <t>2015-06-08</t>
+  </si>
+  <si>
+    <t>Polydor, Universal France</t>
+  </si>
+  <si>
+    <t>Sneazzy, Ed Sheeran, S-Crew, S.Pri Noir, Doums, Amber-Simone featured13, Nemir, Alpha Wann</t>
+  </si>
+  <si>
+    <t>66:35</t>
+  </si>
+  <si>
+    <t>nekfeu-les-etoiles-vagabondes</t>
+  </si>
+  <si>
+    <t>Les étoiles vagabondes</t>
+  </si>
+  <si>
+    <t>breakup, urban, existential, longing, melancholic, death, sentimental, conscious, lonely, serious, political, introspective, poetic, atmospheric, love, male vocalist</t>
+  </si>
+  <si>
+    <t>2019-06-06</t>
+  </si>
+  <si>
+    <t>Polydor, Universal, Universal France</t>
+  </si>
+  <si>
+    <t>Nemir, Vanessa Paradis, Damso, Alpha Wann, Crystal Kay</t>
+  </si>
+  <si>
+    <t>71:43</t>
+  </si>
+  <si>
+    <t>nekfeu-cyborg</t>
+  </si>
+  <si>
+    <t>Cyborg</t>
+  </si>
+  <si>
+    <t>Trap, Cloud Rap, Jazz Rap</t>
+  </si>
+  <si>
+    <t>introspective, urban, conscious, rebellious, alienation, male vocalist, nocturnal, melancholic, serious, technology</t>
+  </si>
+  <si>
+    <t>2016-12-01</t>
+  </si>
+  <si>
+    <t>Clara Luciani, Népal, Murkage Dave, Alpha Wann, Sneazzy, S.Pri Noir, Nemir, 2zer, Mekra, Doums, Malfrat, Jazzy Bazz, Crystal Key featured14</t>
+  </si>
+  <si>
+    <t>Népal, Diabi, Loubenski, Hugz hefner, Hologram Lo', En'zoo producer11, Thomas Vernet producer14</t>
+  </si>
+  <si>
+    <t>60:21</t>
+  </si>
+  <si>
+    <t>laylow-raw-z</t>
+  </si>
+  <si>
+    <t>.RAW-Z</t>
+  </si>
+  <si>
+    <t>cyberpunk, urban, futuristic</t>
+  </si>
+  <si>
+    <t>Wit., Madd featured5</t>
+  </si>
+  <si>
+    <t>34:56</t>
+  </si>
+  <si>
+    <t>booba-lunatic</t>
+  </si>
+  <si>
+    <t>Contemporary R&amp;B, Trap</t>
+  </si>
+  <si>
+    <t>triumphant, boastful, male vocalist</t>
+  </si>
+  <si>
+    <t>2010-11-22</t>
+  </si>
+  <si>
+    <t>Tallac, Because</t>
+  </si>
+  <si>
+    <t>P. Diddy, Akon, 92i, Dosseh, T-Pain, Djé, Ryan Leslie</t>
+  </si>
+  <si>
+    <t>72:27</t>
+  </si>
+  <si>
+    <t>lomepal-jeannine</t>
+  </si>
+  <si>
+    <t>Jeannine</t>
+  </si>
+  <si>
+    <t>Lomepal</t>
+  </si>
+  <si>
+    <t>Alternative R&amp;B, Cloud Rap, Trap Soul</t>
+  </si>
+  <si>
+    <t>lonely, introspective, sentimental, breakup, atmospheric, love, bittersweet, passionate, male vocalist, melancholic</t>
+  </si>
+  <si>
+    <t>[PIAS] France</t>
+  </si>
+  <si>
+    <t>JeanJass, Roméo Elvis, Orelsan, Katerine</t>
+  </si>
+  <si>
+    <t>niska-commando</t>
+  </si>
+  <si>
+    <t>Commando</t>
+  </si>
+  <si>
+    <t>Afro Trap, Hardcore Hip Hop</t>
+  </si>
+  <si>
+    <t>boastful, male vocalist, drugs, urban, rhythmic</t>
+  </si>
+  <si>
+    <t>2017-09-22</t>
+  </si>
+  <si>
+    <t>Booba, MHD, Skaodi</t>
+  </si>
+  <si>
+    <t>mhd-mhd</t>
+  </si>
+  <si>
+    <t>MHD</t>
+  </si>
+  <si>
+    <t>Afro Trap</t>
+  </si>
+  <si>
+    <t>Coupé-décalé, Pop Rap, Afrobeats</t>
+  </si>
+  <si>
+    <t>rhythmic, male vocalist, party, energetic, triumphant, association football, summer</t>
+  </si>
+  <si>
+    <t>2016-04-15</t>
+  </si>
+  <si>
+    <t>Fally Ipupa, Angélique Kidjo</t>
+  </si>
+  <si>
+    <t>columbine-enfants-terribles</t>
+  </si>
+  <si>
+    <t>Enfants terribles</t>
+  </si>
+  <si>
+    <t>Columbine</t>
+  </si>
+  <si>
+    <t>melancholic, male vocalist, urban, lonely, quirky, sarcastic, eclectic, introspective, existential, humorous, love, abstract, bittersweet, sexual, drugs, passionate</t>
+  </si>
+  <si>
+    <t>53:16</t>
+  </si>
+  <si>
+    <t>bigflo-and-oli-la-vraie-vie</t>
+  </si>
+  <si>
+    <t>La vraie vie</t>
+  </si>
+  <si>
+    <t>Bigflo &amp; Oli</t>
+  </si>
+  <si>
+    <t>conscious, fame, male vocalist</t>
+  </si>
+  <si>
+    <t>Joey Starr, Notre père Fabian featured6, Busta Rhymes</t>
+  </si>
+  <si>
+    <t>78:35</t>
+  </si>
+  <si>
+    <t>joke-delorean-music</t>
+  </si>
+  <si>
+    <t>Delorean Music</t>
+  </si>
+  <si>
+    <t>2015-01-01</t>
+  </si>
+  <si>
+    <t>kaaris-or-noir-part-3</t>
+  </si>
+  <si>
+    <t>Or Noir part 3</t>
+  </si>
+  <si>
+    <t>Gangsta Rap, Pop Rap, Hardcore Hip Hop</t>
+  </si>
+  <si>
+    <t>aggressive, drugs, crime, vulgar, male vocalist, urban, boastful</t>
+  </si>
+  <si>
+    <t>2019-01-25</t>
+  </si>
+  <si>
+    <t>Mac Tyer, Sofiane, SCH</t>
+  </si>
+  <si>
+    <t>columbine-clubbing-for-columbine</t>
+  </si>
+  <si>
+    <t>Clubbing for Columbine</t>
+  </si>
+  <si>
+    <t>Electropop, Trap</t>
+  </si>
+  <si>
+    <t>introspective, quirky, sexual, humorous, male vocalist, manic</t>
+  </si>
+  <si>
+    <t>2016-01-01</t>
+  </si>
+  <si>
+    <t>sexion-d-assaut-l-ecole-des-points-vitaux</t>
+  </si>
+  <si>
+    <t>L'école des points vitaux</t>
+  </si>
+  <si>
+    <t>Sexion d'assaut</t>
+  </si>
+  <si>
+    <t>2010-03-29</t>
+  </si>
+  <si>
+    <t>columbine-adieu-bientot</t>
+  </si>
+  <si>
+    <t>Adieu Bientôt</t>
+  </si>
+  <si>
+    <t>Emo Rap, Trap</t>
+  </si>
+  <si>
+    <t>sentimental, introspective, melancholic, love, bittersweet, passionate, drugs, male vocalist, depressive, lonely, sad</t>
+  </si>
+  <si>
+    <t>kaaris-okou-gnakouri</t>
+  </si>
+  <si>
+    <t>Okou Gnakouri</t>
+  </si>
+  <si>
+    <t>Pop Rap, Chicago Drill</t>
+  </si>
+  <si>
+    <t>2016-11-11</t>
+  </si>
+  <si>
+    <t>Gucci Mane, Kalash Criminel</t>
+  </si>
+  <si>
+    <t>Gucci Mane (rap), Kalash Criminel (rap)</t>
+  </si>
+  <si>
+    <t>53:03</t>
+  </si>
+  <si>
+    <t>hugo-tsr-tant-qu-on-est-la</t>
+  </si>
+  <si>
+    <t>Tant qu'on est là</t>
+  </si>
+  <si>
+    <t>Hugo TSR</t>
+  </si>
+  <si>
+    <t>2017-09-20</t>
+  </si>
+  <si>
+    <t>La Chambre Froide</t>
+  </si>
+  <si>
+    <t>37:15</t>
+  </si>
+  <si>
+    <t>hamza-santa-sauce-2</t>
+  </si>
+  <si>
+    <t>Santa Sauce 2</t>
+  </si>
+  <si>
+    <t>Trap, Alternative R&amp;B</t>
+  </si>
+  <si>
+    <t>2019-12-20</t>
+  </si>
+  <si>
+    <t>Damso, Young Adz, Gambi, Koba LaD</t>
+  </si>
+  <si>
+    <t>40:06</t>
+  </si>
+  <si>
+    <t>jul-dans-ma-paranoia</t>
+  </si>
+  <si>
+    <t>Dans ma paranoïa</t>
+  </si>
+  <si>
+    <t>Jul</t>
+  </si>
+  <si>
+    <t>Reggaetón, Trap</t>
+  </si>
+  <si>
+    <t>energetic, male vocalist, rhythmic, urban, introspective, boastful</t>
+  </si>
+  <si>
+    <t>2014-02-24</t>
+  </si>
+  <si>
+    <t>Liga One</t>
+  </si>
+  <si>
+    <t>Kalif Hardcore, Soso Maness</t>
+  </si>
+  <si>
+    <t>60:19</t>
+  </si>
+  <si>
+    <t>jazzy-bazz-nuit</t>
+  </si>
+  <si>
+    <t>Nuit</t>
+  </si>
+  <si>
+    <t>Jazzy Bazz</t>
+  </si>
+  <si>
+    <t>2018-09-07</t>
+  </si>
+  <si>
+    <t>Nekfeu, Sabrina Bellaouel, Lonely Band, Bonnie Banane, Esso Luxueux, Alpha Wann, Monomite</t>
+  </si>
+  <si>
+    <t>Monomite, Kezo producer3, Loubensky producer5-7, The Hop producer8, Fox producer9</t>
+  </si>
+  <si>
+    <t>koba-lad-vii</t>
+  </si>
+  <si>
+    <t>VII</t>
+  </si>
+  <si>
+    <t>Koba LaD</t>
+  </si>
+  <si>
+    <t>crime, drugs, urban, quirky, hedonism, vulgar, male vocalist, violence, boastful</t>
+  </si>
+  <si>
+    <t>Bolémvn featured13, Mafia spartiate</t>
+  </si>
+  <si>
+    <t>niska-mr-sal</t>
+  </si>
+  <si>
+    <t>Mr Sal</t>
+  </si>
+  <si>
+    <t>boastful, urban, male vocalist</t>
+  </si>
+  <si>
+    <t>2019-09-05</t>
+  </si>
+  <si>
+    <t>Millenium</t>
+  </si>
+  <si>
+    <t>Koba LaD, Ninho, Heuss l'Enfoiré, Skaodi, Booba</t>
+  </si>
+  <si>
+    <t>54:05</t>
+  </si>
+  <si>
+    <t>koba-lad-l-affranchi</t>
+  </si>
+  <si>
+    <t>L’Affranchi</t>
+  </si>
+  <si>
+    <t>2019-04-19</t>
+  </si>
+  <si>
+    <t>jul-my-world</t>
+  </si>
+  <si>
+    <t>My World</t>
+  </si>
+  <si>
+    <t>Reggaetón, Gangsta Rap, Hip House</t>
+  </si>
+  <si>
+    <t>party, drugs, male vocalist</t>
+  </si>
+  <si>
+    <t>D'or et de platine</t>
+  </si>
+  <si>
+    <t>70:37</t>
+  </si>
+  <si>
+    <t>roi-heenok-noirs-et-professionnels</t>
+  </si>
+  <si>
+    <t>Noirs et professionnels</t>
+  </si>
+  <si>
+    <t>Roi Heenok</t>
+  </si>
+  <si>
+    <t>Gangsta Rap, Experimental Hip Hop</t>
+  </si>
+  <si>
+    <t>boastful, diss, repetitive, sampling, nocturnal, dark, abstract, urban, lethargic, death, conspiracy, dense, ominous, raw, bassy, violence, alienation, religious, hypnotic, crime, occult, avant-garde, drugs, male vocalist, mysterious</t>
+  </si>
+  <si>
+    <t>2012-12-12</t>
+  </si>
+  <si>
+    <t>Gangster &amp; Gentleman</t>
+  </si>
+  <si>
+    <t>Kinimod, Ugolepatron, Raekwon, James Lescro, G.O.D. Pt. III, Le Gued Muss, Green, Alibi Montana, De Lucci, Mo Labrique featured12, Atlas, Lynn</t>
+  </si>
+  <si>
+    <t>Roi Heenok, Junior Superproducteur, Kinimod, Saincere</t>
+  </si>
+  <si>
+    <t>67:05</t>
+  </si>
+  <si>
+    <t>gims-mon-c-ur-avait-raison</t>
+  </si>
+  <si>
+    <t>Mon cœur avait raison</t>
+  </si>
+  <si>
+    <t>GIMS</t>
+  </si>
+  <si>
+    <t>Pop Rap, French Pop</t>
+  </si>
+  <si>
+    <t>Afrobeats, Latin Pop, Reggaetón</t>
+  </si>
+  <si>
+    <t>rhythmic, melodic, love, male vocalist</t>
+  </si>
+  <si>
+    <t>2015-08-28</t>
+  </si>
+  <si>
+    <t>Wati B, Sony</t>
+  </si>
+  <si>
+    <t>Barack Adama, H-Magnum, Niska, Dadju, Sia, Lefa, Laurent Twins featured2.5, JR O Chrome, Doomams, Insolent, Djuna Family</t>
+  </si>
+  <si>
+    <t>92:21</t>
+  </si>
+  <si>
+    <t>kaaris-dozo</t>
+  </si>
+  <si>
+    <t>Dozo</t>
+  </si>
+  <si>
+    <t>Trap, Afro Trap</t>
+  </si>
+  <si>
+    <t>vulgar, urban, boastful, aggressive, sampling, male vocalist, rhythmic, crime</t>
+  </si>
+  <si>
+    <t>2017-11-03</t>
+  </si>
+  <si>
+    <t>Sofiane, Kalash Criminel</t>
+  </si>
+  <si>
+    <t>54:30</t>
+  </si>
+  <si>
+    <t>gims-subliminal</t>
+  </si>
+  <si>
+    <t>Subliminal</t>
+  </si>
+  <si>
+    <t>2013-05-22</t>
+  </si>
+  <si>
+    <t>Wati B</t>
+  </si>
+  <si>
+    <t>H-Magnum, Black M, JR O Chrome, Dry, Maska, The Shin Sekaï, Dr. Beriz, Insolent, Pitbull, X-Gangs, Beidjik</t>
+  </si>
+  <si>
+    <t>68:46</t>
+  </si>
+  <si>
+    <t>plk-polak</t>
+  </si>
+  <si>
+    <t>Polak</t>
+  </si>
+  <si>
+    <t>PLK</t>
+  </si>
+  <si>
+    <t>2018-10-05</t>
+  </si>
+  <si>
+    <t>Panenka</t>
+  </si>
+  <si>
+    <t>Nekfeu, Paluch, SCH, Yseult</t>
+  </si>
+  <si>
+    <t>Junior Alaprod, Katrina Squad, Marlin, Yseult, Yung G</t>
+  </si>
+  <si>
+    <t>Nekfeu (rap), Paluch (rap), SCH (rap), Yseult (vocals)</t>
+  </si>
+  <si>
+    <t>20cent Audou (mixage), Éric Chevet (mastering)</t>
+  </si>
+  <si>
+    <t>Fifou (cover art)</t>
+  </si>
+  <si>
+    <t>jazzy-bazz-p-town</t>
+  </si>
+  <si>
+    <t>P-Town</t>
+  </si>
+  <si>
+    <t>2016-02-26</t>
+  </si>
+  <si>
+    <t>Freddie Gibbs, Esso Luxueux, Bonnie Banane</t>
+  </si>
+  <si>
+    <t>55:44</t>
+  </si>
+  <si>
+    <t>triplego-machakil</t>
+  </si>
+  <si>
+    <t>MACHAKIL</t>
+  </si>
+  <si>
+    <t>nocturnal, sampling, lethargic, sparse, ethereal, apathetic, male vocalist, drugs, mellow</t>
+  </si>
+  <si>
+    <t>2019-03-07</t>
+  </si>
+  <si>
+    <t>61:30</t>
+  </si>
+  <si>
+    <t>jazzy-bazz-sur-la-route-du-3-14</t>
+  </si>
+  <si>
+    <t>Sur La Route Du 3.14</t>
+  </si>
+  <si>
+    <t>sampling, rhythmic, male vocalist</t>
+  </si>
+  <si>
+    <t>2012-07-16</t>
+  </si>
+  <si>
+    <t>Esso Luxueux, Deen Burbigo, Kema featured4, L’Etrange featured7, Nekfeu, Alpha Wann</t>
+  </si>
+  <si>
+    <t>28:37</t>
+  </si>
+  <si>
+    <t>alkpote-and-butter-bullets-tenebreuse-musique</t>
+  </si>
+  <si>
+    <t>Ténébreuse musique</t>
+  </si>
+  <si>
+    <t>Alkpote &amp; Butter Bullets</t>
+  </si>
+  <si>
+    <t>crime, misanthropic, vulgar, surreal, anxious, sampling, nocturnal, dark, hateful, aggressive, menacing, energetic, depressive, dense, ominous, rhythmic, raw, sexual, technical, sombre, atmospheric, drugs, boastful, male vocalist, manic, futuristic</t>
+  </si>
+  <si>
+    <t>2016-01-20</t>
+  </si>
+  <si>
+    <t>Hamza, Jok'air, K-Luv featured9</t>
+  </si>
+  <si>
+    <t>Singemongol executive producer</t>
+  </si>
+  <si>
+    <t>Singemongol executive producer (artwork), Stephen Vuillemin (logo designer), Qoso (logo designer)</t>
+  </si>
+  <si>
+    <t>jul-rien-100-rien</t>
+  </si>
+  <si>
+    <t>Rien 100 rien</t>
+  </si>
+  <si>
+    <t>Afro Trap, Hip House, Reggaetón, Trap</t>
+  </si>
+  <si>
+    <t>2019-06-14</t>
+  </si>
+  <si>
+    <t>Ninho, TK, Heuss l'Enfoiré, Vald, Moubarak, Mula B, La Famax</t>
+  </si>
+  <si>
+    <t>jul-l-ovni</t>
+  </si>
+  <si>
+    <t>L'ovni</t>
+  </si>
+  <si>
+    <t>Pop Rap, Hip House</t>
+  </si>
+  <si>
+    <t>Reggaetón</t>
+  </si>
+  <si>
+    <t>76:00</t>
+  </si>
+  <si>
+    <t>gradur-l-homme-au-bob</t>
+  </si>
+  <si>
+    <t>L'homme au bob</t>
+  </si>
+  <si>
+    <t>Gradur</t>
+  </si>
+  <si>
+    <t>aggressive, boastful, male vocalist</t>
+  </si>
+  <si>
+    <t>2015-02-23</t>
+  </si>
+  <si>
+    <t>Alonzo, Niro, Chief Keef, Lacrim, Migos, Kayna Samet</t>
+  </si>
+  <si>
+    <t>alkpote-inferno</t>
+  </si>
+  <si>
+    <t>Alkpote</t>
+  </si>
+  <si>
+    <t>heuss-l-enfoire-en-esprit</t>
+  </si>
+  <si>
+    <t>En esprit</t>
+  </si>
+  <si>
+    <t>Heuss l'Enfoiré</t>
+  </si>
+  <si>
+    <t>Pop Rap, Gangsta Rap, Trap</t>
+  </si>
+  <si>
+    <t>party, crime, urban, male vocalist, drugs, boastful</t>
+  </si>
+  <si>
+    <t>Koba LaD, Sofiane, Soolking, Vald</t>
+  </si>
+  <si>
+    <t>44:51</t>
+  </si>
+  <si>
+    <t>1995-paris-sud-minute</t>
+  </si>
+  <si>
+    <t>Paris Sud minute</t>
+  </si>
+  <si>
+    <t>sampling, urban, bittersweet, drugs, boastful, male vocalist</t>
+  </si>
+  <si>
+    <t>2012-12</t>
+  </si>
+  <si>
+    <t>plk-mental</t>
+  </si>
+  <si>
+    <t>Mental</t>
+  </si>
+  <si>
+    <t>Pop Rap, Reggaetón</t>
+  </si>
+  <si>
+    <t>2019-09-13</t>
+  </si>
+  <si>
+    <t>Timal, Tessa B featured9, Aladin 135, Maes</t>
+  </si>
+  <si>
+    <t>black-m-les-yeux-plus-gros-que-le-monde</t>
+  </si>
+  <si>
+    <t>Les yeux plus gros que le monde</t>
+  </si>
+  <si>
+    <t>Black M</t>
+  </si>
+  <si>
+    <t>French Pop</t>
+  </si>
+  <si>
+    <t>2014-03-31</t>
+  </si>
+  <si>
+    <t>Jr O Crom, Dry, Big Ali, Dr. Beriz, The Shin Sekaï, Doomams</t>
+  </si>
+  <si>
+    <t>76:39</t>
+  </si>
+  <si>
+    <t>jul-je-ne-me-vois-pas-briller</t>
+  </si>
+  <si>
+    <t>Je ne me vois pas briller</t>
+  </si>
+  <si>
+    <t>Le Rat Luciano, Moubarak, Norey Fz featured15, Kalash Criminel, Hors Ligne featured20, Ger featured23</t>
+  </si>
+  <si>
+    <t>alkpote-and-luv-resval-mariah</t>
+  </si>
+  <si>
+    <t>Mariah</t>
+  </si>
+  <si>
+    <t>Alkpote &amp; Luv Resval</t>
+  </si>
+  <si>
+    <t>heavy, mellow, vulgar, surreal, anxious, sampling, dark, aggressive, cold, energetic, bouncy, ominous, rhythmic, bassy, sexual, money, melodic, atmospheric, drugs, boastful, male vocalist, futuristic, hypnotic</t>
+  </si>
+  <si>
+    <t>2018-12-21</t>
+  </si>
+  <si>
+    <t>17:03</t>
+  </si>
+  <si>
+    <t>kekra-freebase-vol-1</t>
+  </si>
+  <si>
+    <t>Freebase Vol. 1</t>
+  </si>
+  <si>
+    <t>2015-10-10</t>
+  </si>
+  <si>
+    <t>DJ E-Rise, Charisma additional producer1, Blackstarz producer4, Killogrammes Prod producer9, Djazzi</t>
+  </si>
+  <si>
+    <t>48:55</t>
+  </si>
+  <si>
+    <t>jul-la-zone-en-personne</t>
+  </si>
+  <si>
+    <t>La zone en personne</t>
+  </si>
+  <si>
+    <t>Reggaetón, Hardcore Hip Hop</t>
+  </si>
+  <si>
+    <t>Alonzo, Soolking, Landy, Gambino, ZackMess featured1.16, Metah featured1.16, Oscar featured1.16, Miklo featured1.16, Moubarak, TK, Djenna Della featured1.17, GIMS, Loredana featured2.6, Ninho</t>
+  </si>
+  <si>
+    <t>jok-air-jok-travolta</t>
+  </si>
+  <si>
+    <t>Jok'Travolta</t>
+  </si>
+  <si>
+    <t>Har2Nok</t>
+  </si>
+  <si>
+    <t>79:50</t>
+  </si>
+  <si>
+    <t>sofiane-bandit-salete</t>
+  </si>
+  <si>
+    <t>Bandit saleté</t>
+  </si>
+  <si>
+    <t>crime, vulgar, male vocalist</t>
+  </si>
+  <si>
+    <t>2017-05-12</t>
+  </si>
+  <si>
+    <t>Capitol Music France, Suther Kane</t>
+  </si>
+  <si>
+    <t>YL, Bakyl, Samat, GLK, Hornet la Frappe</t>
+  </si>
+  <si>
+    <t>49:35</t>
+  </si>
+  <si>
+    <t>sofiane-affranchis</t>
+  </si>
+  <si>
+    <t>Affranchis</t>
+  </si>
+  <si>
+    <t>2018-01-26</t>
+  </si>
+  <si>
+    <t>kalash-criminel-oyoki</t>
+  </si>
+  <si>
+    <t>Oyoki</t>
+  </si>
+  <si>
+    <t>Hardcore Hip Hop, Trap, Drill</t>
+  </si>
+  <si>
+    <t>2017-05-19</t>
+  </si>
+  <si>
+    <t>Douma featured5, Jul, Mac Tyer, Sofiane, Vald, Keblack</t>
+  </si>
+  <si>
+    <t>Glové performer6 (performer), Docks performer11 (performer)</t>
+  </si>
+  <si>
+    <t>53:04</t>
+  </si>
+  <si>
+    <t>93-empire-93-empire</t>
+  </si>
+  <si>
+    <t>93 Empire</t>
+  </si>
+  <si>
+    <t>crime, vulgar, posse cut, hateful, urban, aggressive, violence, boastful, male vocalist</t>
+  </si>
+  <si>
+    <t>la-fouine-la-fouine-vs-laouni</t>
+  </si>
+  <si>
+    <t>La Fouine vs Laouni</t>
+  </si>
+  <si>
+    <t>La Fouine</t>
+  </si>
+  <si>
+    <t>Pop Rap, Conscious Hip Hop, Hardcore Hip Hop, Trap</t>
+  </si>
+  <si>
+    <t>introspective, boastful, male vocalist</t>
+  </si>
+  <si>
+    <t>2011-02-14</t>
+  </si>
+  <si>
+    <t>Rohff, Seth Gueko, Admiral T, Canardo, Nessbeal, Evaanz, Game, Zaho, Leïla, Soprano</t>
+  </si>
+  <si>
+    <t>DJ Battle (host)</t>
+  </si>
+  <si>
+    <t>103:32</t>
+  </si>
+  <si>
+    <t>niska-zifukoro</t>
+  </si>
+  <si>
+    <t>Zifukoro</t>
+  </si>
+  <si>
+    <t>Pop Rap, Afro Trap</t>
+  </si>
+  <si>
+    <t>2016-06-03</t>
+  </si>
+  <si>
+    <t>Booba, Kalash, GIMS, SCH, Sidiki Diabaté, Gradur, Madrane, Skaodi, La B featured18, Trafiquinte</t>
+  </si>
+  <si>
+    <t>71:56</t>
+  </si>
+  <si>
+    <t>ashe-22-ashe-tape-vol-1</t>
+  </si>
+  <si>
+    <t>Ashe Tape, vol. 1</t>
+  </si>
+  <si>
+    <t>ASHE 22</t>
+  </si>
+  <si>
+    <t>No Melody</t>
+  </si>
+  <si>
+    <t>minimalistic, sexual, romantic, vulgar, melodic, drugs, ominous, deadpan</t>
+  </si>
+  <si>
+    <t>2019-03-08</t>
+  </si>
+  <si>
+    <t>Zeu, Gouap, Kpri, Juice featured11, Mini Gouap featured11</t>
+  </si>
+  <si>
+    <t>31:03</t>
+  </si>
+  <si>
+    <t>myth-syzer-bisous-mortels</t>
+  </si>
+  <si>
+    <t>Bisous mortels</t>
+  </si>
+  <si>
+    <t>2018-11-30</t>
+  </si>
+  <si>
+    <t>OldPee, Ateyaba, Lino, Zed, Zefor, Alkpote, Jok'air, Ichon, Loveni, Hamza, Leto, Take a Mic, Di-Meh, Slimka</t>
+  </si>
+  <si>
+    <t>36:22</t>
+  </si>
+  <si>
+    <t>la-fouine-drole-de-parcours</t>
+  </si>
+  <si>
+    <t>Drôle de parcours</t>
+  </si>
+  <si>
+    <t>2013-02-04</t>
+  </si>
+  <si>
+    <t>Zaho, Canardo, Youssoupha, Niro, Sultan, Fababy, Amel Bent, Corneille, Mac Tyer, French Montana</t>
+  </si>
+  <si>
+    <t>74:42</t>
+  </si>
+  <si>
+    <t>disiz-transe-lucide</t>
+  </si>
+  <si>
+    <t>Transe-lucide</t>
+  </si>
+  <si>
+    <t>2014-03-03</t>
+  </si>
+  <si>
+    <t>georgio-bleu-noir</t>
+  </si>
+  <si>
+    <t>Bleu noir</t>
+  </si>
+  <si>
+    <t>Georgio</t>
+  </si>
+  <si>
+    <t>urban, melancholic, poetic, rebellious, introspective, male vocalist, depressive, conscious</t>
+  </si>
+  <si>
+    <t>Iron Sy, Sanka featured10, Elisa Jo</t>
+  </si>
+  <si>
+    <t>58:09</t>
+  </si>
+  <si>
+    <t>georgio-hera</t>
+  </si>
+  <si>
+    <t>Héra</t>
+  </si>
+  <si>
+    <t>bittersweet, conscious, triumphant, warm, sentimental, male vocalist, passionate</t>
+  </si>
+  <si>
+    <t>43:49</t>
+  </si>
+  <si>
+    <t>jok-air-jok-rambo</t>
+  </si>
+  <si>
+    <t>Jok'Rambo</t>
+  </si>
+  <si>
+    <t>French Pop, Trap Soul</t>
+  </si>
+  <si>
+    <t>sexual</t>
+  </si>
+  <si>
+    <t>2018-05-25</t>
+  </si>
+  <si>
+    <t>DJ Weedim, Medeline</t>
+  </si>
+  <si>
+    <t>Madame Monsieur (vocals)</t>
+  </si>
+  <si>
+    <t>67:19</t>
+  </si>
+  <si>
+    <t>dosseh-vidalo-a</t>
+  </si>
+  <si>
+    <t>Vidalo$$a</t>
+  </si>
+  <si>
+    <t>2018-07-06</t>
+  </si>
+  <si>
+    <t>56:32</t>
+  </si>
+  <si>
+    <t>plk-tenebreux</t>
+  </si>
+  <si>
+    <t>Ténébreux</t>
+  </si>
+  <si>
+    <t>2017-09-08</t>
+  </si>
+  <si>
+    <t>Krisy</t>
+  </si>
+  <si>
+    <t>37:39</t>
+  </si>
+  <si>
+    <t>youv-dee-gear-2</t>
+  </si>
+  <si>
+    <t>Gear 2</t>
+  </si>
+  <si>
+    <t>Youv Dee</t>
+  </si>
+  <si>
+    <t>Pop Rap, Cloud Rap, Trap Metal</t>
+  </si>
+  <si>
+    <t>2017-12-15</t>
+  </si>
+  <si>
+    <t>Arsn rap10, Sirap rap10</t>
+  </si>
+  <si>
+    <t>Arsn rap10 (rap), Sirap rap10 (rap)</t>
+  </si>
+  <si>
+    <t>32:43</t>
+  </si>
+  <si>
+    <t>koba-lad-tenebreux</t>
+  </si>
+  <si>
+    <t>2018-05-11</t>
+  </si>
+  <si>
+    <t>Jewfy producer1, BricksOnDaBeat, Laytebeats producer3, Million Man producer4, Sassori producer6</t>
+  </si>
+  <si>
+    <t>17:12</t>
+  </si>
+  <si>
+    <t>zuukou-mayzie-j-m-u-a-z</t>
+  </si>
+  <si>
+    <t>J.M.U.A.Z</t>
+  </si>
+  <si>
+    <t>Trap, Progressive Electronic</t>
+  </si>
+  <si>
+    <t>Lala &amp;ce, Oklou, Freeze Corleone</t>
+  </si>
+  <si>
+    <t>29:23</t>
   </si>
 </sst>
 </file>
@@ -23208,7 +24447,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:AA746"/>
+  <dimension ref="A1:AA815"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" style="2" bestFit="1" customWidth="1"/>
@@ -70847,6 +72086,4041 @@
         <v>16</v>
       </c>
     </row>
+    <row r="747" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A747" s="13" t="s">
+        <v>7581</v>
+      </c>
+      <c r="B747" s="13" t="s">
+        <v>7582</v>
+      </c>
+      <c r="C747" s="13" t="s">
+        <v>7583</v>
+      </c>
+      <c r="D747" s="14">
+        <v>2010</v>
+      </c>
+      <c r="E747" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F747" s="14"/>
+      <c r="G747" s="13" t="s">
+        <v>7584</v>
+      </c>
+      <c r="H747" s="13" t="s">
+        <v>7585</v>
+      </c>
+      <c r="I747" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J747" s="13" t="s">
+        <v>7586</v>
+      </c>
+      <c r="K747" s="14"/>
+      <c r="L747" s="14"/>
+      <c r="M747" s="14"/>
+      <c r="N747" s="14"/>
+      <c r="O747" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P747" s="13" t="s">
+        <v>7587</v>
+      </c>
+      <c r="Q747" s="13" t="s">
+        <v>2836</v>
+      </c>
+      <c r="R747" s="13" t="s">
+        <v>5457</v>
+      </c>
+      <c r="S747" s="13" t="s">
+        <v>7588</v>
+      </c>
+      <c r="T747" s="14"/>
+      <c r="U747" s="13" t="s">
+        <v>7589</v>
+      </c>
+      <c r="V747" s="14"/>
+      <c r="W747" s="13" t="s">
+        <v>7590</v>
+      </c>
+      <c r="X747" s="13" t="s">
+        <v>7591</v>
+      </c>
+      <c r="Y747" s="13" t="s">
+        <v>7592</v>
+      </c>
+      <c r="Z747" s="13" t="s">
+        <v>7593</v>
+      </c>
+      <c r="AA747" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="748" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A748" s="13" t="s">
+        <v>7594</v>
+      </c>
+      <c r="B748" s="13" t="s">
+        <v>7595</v>
+      </c>
+      <c r="C748" s="13" t="s">
+        <v>5542</v>
+      </c>
+      <c r="D748" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E748" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F748" s="14"/>
+      <c r="G748" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H748" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="I748" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J748" s="13" t="s">
+        <v>7596</v>
+      </c>
+      <c r="K748" s="14"/>
+      <c r="L748" s="14"/>
+      <c r="M748" s="14"/>
+      <c r="N748" s="14"/>
+      <c r="O748" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P748" s="13" t="s">
+        <v>7597</v>
+      </c>
+      <c r="Q748" s="14"/>
+      <c r="R748" s="14"/>
+      <c r="S748" s="13" t="s">
+        <v>5545</v>
+      </c>
+      <c r="T748" s="14"/>
+      <c r="U748" s="14"/>
+      <c r="V748" s="14"/>
+      <c r="W748" s="14"/>
+      <c r="X748" s="14"/>
+      <c r="Y748" s="14"/>
+      <c r="Z748" s="13" t="s">
+        <v>7598</v>
+      </c>
+      <c r="AA748" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="749" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A749" s="13" t="s">
+        <v>7599</v>
+      </c>
+      <c r="B749" s="13" t="s">
+        <v>7600</v>
+      </c>
+      <c r="C749" s="13" t="s">
+        <v>7601</v>
+      </c>
+      <c r="D749" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E749" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F749" s="14"/>
+      <c r="G749" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H749" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I749" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J749" s="13" t="s">
+        <v>7602</v>
+      </c>
+      <c r="K749" s="14"/>
+      <c r="L749" s="14"/>
+      <c r="M749" s="14"/>
+      <c r="N749" s="14"/>
+      <c r="O749" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P749" s="13" t="s">
+        <v>7603</v>
+      </c>
+      <c r="Q749" s="14"/>
+      <c r="R749" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S749" s="13" t="s">
+        <v>7604</v>
+      </c>
+      <c r="T749" s="13" t="s">
+        <v>7605</v>
+      </c>
+      <c r="U749" s="14"/>
+      <c r="V749" s="14"/>
+      <c r="W749" s="14"/>
+      <c r="X749" s="14"/>
+      <c r="Y749" s="14"/>
+      <c r="Z749" s="13" t="s">
+        <v>7606</v>
+      </c>
+      <c r="AA749" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="750" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+      <c r="A750" s="13" t="s">
+        <v>7607</v>
+      </c>
+      <c r="B750" s="13" t="s">
+        <v>7608</v>
+      </c>
+      <c r="C750" s="13" t="s">
+        <v>7601</v>
+      </c>
+      <c r="D750" s="14">
+        <v>2011</v>
+      </c>
+      <c r="E750" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F750" s="14"/>
+      <c r="G750" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H750" s="13" t="s">
+        <v>7609</v>
+      </c>
+      <c r="I750" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J750" s="13" t="s">
+        <v>7610</v>
+      </c>
+      <c r="K750" s="14"/>
+      <c r="L750" s="14"/>
+      <c r="M750" s="14"/>
+      <c r="N750" s="14"/>
+      <c r="O750" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P750" s="13" t="s">
+        <v>7611</v>
+      </c>
+      <c r="Q750" s="14"/>
+      <c r="R750" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S750" s="13" t="s">
+        <v>7612</v>
+      </c>
+      <c r="T750" s="13" t="s">
+        <v>7613</v>
+      </c>
+      <c r="U750" s="14"/>
+      <c r="V750" s="14"/>
+      <c r="W750" s="14"/>
+      <c r="X750" s="14"/>
+      <c r="Y750" s="14"/>
+      <c r="Z750" s="13" t="s">
+        <v>7614</v>
+      </c>
+      <c r="AA750" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="751" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+      <c r="A751" s="13" t="s">
+        <v>7615</v>
+      </c>
+      <c r="B751" s="13" t="s">
+        <v>7616</v>
+      </c>
+      <c r="C751" s="13" t="s">
+        <v>5831</v>
+      </c>
+      <c r="D751" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E751" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F751" s="14"/>
+      <c r="G751" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H751" s="13" t="s">
+        <v>2173</v>
+      </c>
+      <c r="I751" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J751" s="13" t="s">
+        <v>7617</v>
+      </c>
+      <c r="K751" s="14"/>
+      <c r="L751" s="14"/>
+      <c r="M751" s="14"/>
+      <c r="N751" s="14"/>
+      <c r="O751" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P751" s="13" t="s">
+        <v>7618</v>
+      </c>
+      <c r="Q751" s="14"/>
+      <c r="R751" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S751" s="13" t="s">
+        <v>5834</v>
+      </c>
+      <c r="T751" s="13" t="s">
+        <v>7619</v>
+      </c>
+      <c r="U751" s="14"/>
+      <c r="V751" s="14"/>
+      <c r="W751" s="14"/>
+      <c r="X751" s="14"/>
+      <c r="Y751" s="14"/>
+      <c r="Z751" s="13" t="s">
+        <v>7620</v>
+      </c>
+      <c r="AA751" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="752" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A752" s="13" t="s">
+        <v>7621</v>
+      </c>
+      <c r="B752" s="13" t="s">
+        <v>7622</v>
+      </c>
+      <c r="C752" s="13" t="s">
+        <v>7623</v>
+      </c>
+      <c r="D752" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E752" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F752" s="14"/>
+      <c r="G752" s="13" t="s">
+        <v>7283</v>
+      </c>
+      <c r="H752" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I752" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J752" s="13" t="s">
+        <v>7624</v>
+      </c>
+      <c r="K752" s="14"/>
+      <c r="L752" s="14"/>
+      <c r="M752" s="14"/>
+      <c r="N752" s="14"/>
+      <c r="O752" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P752" s="13" t="s">
+        <v>7625</v>
+      </c>
+      <c r="Q752" s="14"/>
+      <c r="R752" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S752" s="13" t="s">
+        <v>7626</v>
+      </c>
+      <c r="T752" s="13" t="s">
+        <v>7627</v>
+      </c>
+      <c r="U752" s="14"/>
+      <c r="V752" s="14"/>
+      <c r="W752" s="14"/>
+      <c r="X752" s="14"/>
+      <c r="Y752" s="14"/>
+      <c r="Z752" s="13" t="s">
+        <v>7628</v>
+      </c>
+      <c r="AA752" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="753" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A753" s="13" t="s">
+        <v>7629</v>
+      </c>
+      <c r="B753" s="13" t="s">
+        <v>7630</v>
+      </c>
+      <c r="C753" s="13" t="s">
+        <v>7623</v>
+      </c>
+      <c r="D753" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E753" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F753" s="14"/>
+      <c r="G753" s="13" t="s">
+        <v>6235</v>
+      </c>
+      <c r="H753" s="13" t="s">
+        <v>5648</v>
+      </c>
+      <c r="I753" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J753" s="13" t="s">
+        <v>7631</v>
+      </c>
+      <c r="K753" s="14"/>
+      <c r="L753" s="14"/>
+      <c r="M753" s="14"/>
+      <c r="N753" s="14"/>
+      <c r="O753" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P753" s="13" t="s">
+        <v>7632</v>
+      </c>
+      <c r="Q753" s="14"/>
+      <c r="R753" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S753" s="13" t="s">
+        <v>7633</v>
+      </c>
+      <c r="T753" s="13" t="s">
+        <v>7634</v>
+      </c>
+      <c r="U753" s="14"/>
+      <c r="V753" s="14"/>
+      <c r="W753" s="14"/>
+      <c r="X753" s="14"/>
+      <c r="Y753" s="14"/>
+      <c r="Z753" s="13" t="s">
+        <v>7635</v>
+      </c>
+      <c r="AA753" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="754" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+      <c r="A754" s="13" t="s">
+        <v>7636</v>
+      </c>
+      <c r="B754" s="13" t="s">
+        <v>7637</v>
+      </c>
+      <c r="C754" s="13" t="s">
+        <v>7623</v>
+      </c>
+      <c r="D754" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E754" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F754" s="14"/>
+      <c r="G754" s="13" t="s">
+        <v>2173</v>
+      </c>
+      <c r="H754" s="13" t="s">
+        <v>7638</v>
+      </c>
+      <c r="I754" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J754" s="13" t="s">
+        <v>7639</v>
+      </c>
+      <c r="K754" s="14"/>
+      <c r="L754" s="14"/>
+      <c r="M754" s="14"/>
+      <c r="N754" s="14"/>
+      <c r="O754" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P754" s="13" t="s">
+        <v>7640</v>
+      </c>
+      <c r="Q754" s="14"/>
+      <c r="R754" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S754" s="13" t="s">
+        <v>899</v>
+      </c>
+      <c r="T754" s="13" t="s">
+        <v>7641</v>
+      </c>
+      <c r="U754" s="13" t="s">
+        <v>7642</v>
+      </c>
+      <c r="V754" s="14"/>
+      <c r="W754" s="14"/>
+      <c r="X754" s="14"/>
+      <c r="Y754" s="14"/>
+      <c r="Z754" s="13" t="s">
+        <v>7643</v>
+      </c>
+      <c r="AA754" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="755" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A755" s="13" t="s">
+        <v>7644</v>
+      </c>
+      <c r="B755" s="13" t="s">
+        <v>7645</v>
+      </c>
+      <c r="C755" s="13" t="s">
+        <v>5647</v>
+      </c>
+      <c r="D755" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E755" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F755" s="14"/>
+      <c r="G755" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H755" s="13" t="s">
+        <v>6178</v>
+      </c>
+      <c r="I755" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J755" s="13" t="s">
+        <v>7646</v>
+      </c>
+      <c r="K755" s="14"/>
+      <c r="L755" s="14"/>
+      <c r="M755" s="14"/>
+      <c r="N755" s="14"/>
+      <c r="O755" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P755" s="13" t="s">
+        <v>6026</v>
+      </c>
+      <c r="Q755" s="14"/>
+      <c r="R755" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S755" s="14"/>
+      <c r="T755" s="13" t="s">
+        <v>7647</v>
+      </c>
+      <c r="U755" s="14"/>
+      <c r="V755" s="14"/>
+      <c r="W755" s="14"/>
+      <c r="X755" s="14"/>
+      <c r="Y755" s="14"/>
+      <c r="Z755" s="13" t="s">
+        <v>7648</v>
+      </c>
+      <c r="AA755" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="756" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A756" s="13" t="s">
+        <v>7649</v>
+      </c>
+      <c r="B756" s="13" t="s">
+        <v>6640</v>
+      </c>
+      <c r="C756" s="13" t="s">
+        <v>3691</v>
+      </c>
+      <c r="D756" s="14">
+        <v>2010</v>
+      </c>
+      <c r="E756" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F756" s="14"/>
+      <c r="G756" s="13" t="s">
+        <v>6130</v>
+      </c>
+      <c r="H756" s="13" t="s">
+        <v>7650</v>
+      </c>
+      <c r="I756" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J756" s="13" t="s">
+        <v>7651</v>
+      </c>
+      <c r="K756" s="14"/>
+      <c r="L756" s="14"/>
+      <c r="M756" s="14"/>
+      <c r="N756" s="14"/>
+      <c r="O756" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P756" s="13" t="s">
+        <v>7652</v>
+      </c>
+      <c r="Q756" s="14"/>
+      <c r="R756" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S756" s="13" t="s">
+        <v>7653</v>
+      </c>
+      <c r="T756" s="13" t="s">
+        <v>7654</v>
+      </c>
+      <c r="U756" s="14"/>
+      <c r="V756" s="14"/>
+      <c r="W756" s="14"/>
+      <c r="X756" s="14"/>
+      <c r="Y756" s="14"/>
+      <c r="Z756" s="13" t="s">
+        <v>7655</v>
+      </c>
+      <c r="AA756" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="757" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A757" s="13" t="s">
+        <v>7656</v>
+      </c>
+      <c r="B757" s="13" t="s">
+        <v>7657</v>
+      </c>
+      <c r="C757" s="13" t="s">
+        <v>7658</v>
+      </c>
+      <c r="D757" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E757" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F757" s="14"/>
+      <c r="G757" s="13" t="s">
+        <v>2846</v>
+      </c>
+      <c r="H757" s="13" t="s">
+        <v>7659</v>
+      </c>
+      <c r="I757" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J757" s="13" t="s">
+        <v>7660</v>
+      </c>
+      <c r="K757" s="14"/>
+      <c r="L757" s="14"/>
+      <c r="M757" s="14"/>
+      <c r="N757" s="14"/>
+      <c r="O757" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P757" s="13" t="s">
+        <v>6026</v>
+      </c>
+      <c r="Q757" s="14"/>
+      <c r="R757" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S757" s="13" t="s">
+        <v>7661</v>
+      </c>
+      <c r="T757" s="13" t="s">
+        <v>7662</v>
+      </c>
+      <c r="U757" s="14"/>
+      <c r="V757" s="14"/>
+      <c r="W757" s="14"/>
+      <c r="X757" s="14"/>
+      <c r="Y757" s="14"/>
+      <c r="Z757" s="13" t="s">
+        <v>6223</v>
+      </c>
+      <c r="AA757" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="758" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A758" s="13" t="s">
+        <v>7663</v>
+      </c>
+      <c r="B758" s="13" t="s">
+        <v>7664</v>
+      </c>
+      <c r="C758" s="13" t="s">
+        <v>6142</v>
+      </c>
+      <c r="D758" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E758" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F758" s="14"/>
+      <c r="G758" s="13" t="s">
+        <v>5380</v>
+      </c>
+      <c r="H758" s="13" t="s">
+        <v>7665</v>
+      </c>
+      <c r="I758" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J758" s="13" t="s">
+        <v>7666</v>
+      </c>
+      <c r="K758" s="14"/>
+      <c r="L758" s="14"/>
+      <c r="M758" s="14"/>
+      <c r="N758" s="14"/>
+      <c r="O758" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P758" s="13" t="s">
+        <v>7667</v>
+      </c>
+      <c r="Q758" s="14"/>
+      <c r="R758" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S758" s="14"/>
+      <c r="T758" s="13" t="s">
+        <v>7668</v>
+      </c>
+      <c r="U758" s="14"/>
+      <c r="V758" s="14"/>
+      <c r="W758" s="14"/>
+      <c r="X758" s="14"/>
+      <c r="Y758" s="14"/>
+      <c r="Z758" s="14"/>
+      <c r="AA758" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="759" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A759" s="13" t="s">
+        <v>7669</v>
+      </c>
+      <c r="B759" s="13" t="s">
+        <v>7670</v>
+      </c>
+      <c r="C759" s="13" t="s">
+        <v>7670</v>
+      </c>
+      <c r="D759" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E759" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F759" s="14"/>
+      <c r="G759" s="13" t="s">
+        <v>7671</v>
+      </c>
+      <c r="H759" s="13" t="s">
+        <v>7672</v>
+      </c>
+      <c r="I759" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J759" s="13" t="s">
+        <v>7673</v>
+      </c>
+      <c r="K759" s="14"/>
+      <c r="L759" s="14"/>
+      <c r="M759" s="14"/>
+      <c r="N759" s="14"/>
+      <c r="O759" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P759" s="13" t="s">
+        <v>7674</v>
+      </c>
+      <c r="Q759" s="14"/>
+      <c r="R759" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S759" s="14"/>
+      <c r="T759" s="13" t="s">
+        <v>7675</v>
+      </c>
+      <c r="U759" s="14"/>
+      <c r="V759" s="14"/>
+      <c r="W759" s="14"/>
+      <c r="X759" s="14"/>
+      <c r="Y759" s="14"/>
+      <c r="Z759" s="14"/>
+      <c r="AA759" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="760" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+      <c r="A760" s="13" t="s">
+        <v>7676</v>
+      </c>
+      <c r="B760" s="13" t="s">
+        <v>7677</v>
+      </c>
+      <c r="C760" s="13" t="s">
+        <v>7678</v>
+      </c>
+      <c r="D760" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E760" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F760" s="14"/>
+      <c r="G760" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H760" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="I760" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J760" s="13" t="s">
+        <v>7679</v>
+      </c>
+      <c r="K760" s="14"/>
+      <c r="L760" s="14"/>
+      <c r="M760" s="14"/>
+      <c r="N760" s="14"/>
+      <c r="O760" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P760" s="13" t="s">
+        <v>5812</v>
+      </c>
+      <c r="Q760" s="14"/>
+      <c r="R760" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S760" s="14"/>
+      <c r="T760" s="14"/>
+      <c r="U760" s="14"/>
+      <c r="V760" s="14"/>
+      <c r="W760" s="14"/>
+      <c r="X760" s="14"/>
+      <c r="Y760" s="14"/>
+      <c r="Z760" s="13" t="s">
+        <v>7680</v>
+      </c>
+      <c r="AA760" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="761" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A761" s="13" t="s">
+        <v>7681</v>
+      </c>
+      <c r="B761" s="13" t="s">
+        <v>7682</v>
+      </c>
+      <c r="C761" s="13" t="s">
+        <v>7683</v>
+      </c>
+      <c r="D761" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E761" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F761" s="14"/>
+      <c r="G761" s="13" t="s">
+        <v>7283</v>
+      </c>
+      <c r="H761" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="I761" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J761" s="13" t="s">
+        <v>7684</v>
+      </c>
+      <c r="K761" s="14"/>
+      <c r="L761" s="14"/>
+      <c r="M761" s="14"/>
+      <c r="N761" s="14"/>
+      <c r="O761" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P761" s="13" t="s">
+        <v>4749</v>
+      </c>
+      <c r="Q761" s="14"/>
+      <c r="R761" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S761" s="13" t="s">
+        <v>899</v>
+      </c>
+      <c r="T761" s="13" t="s">
+        <v>7685</v>
+      </c>
+      <c r="U761" s="14"/>
+      <c r="V761" s="14"/>
+      <c r="W761" s="14"/>
+      <c r="X761" s="14"/>
+      <c r="Y761" s="14"/>
+      <c r="Z761" s="13" t="s">
+        <v>7686</v>
+      </c>
+      <c r="AA761" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="762" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A762" s="13" t="s">
+        <v>7687</v>
+      </c>
+      <c r="B762" s="13" t="s">
+        <v>7688</v>
+      </c>
+      <c r="C762" s="13" t="s">
+        <v>5606</v>
+      </c>
+      <c r="D762" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E762" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F762" s="14"/>
+      <c r="G762" s="13" t="s">
+        <v>6358</v>
+      </c>
+      <c r="H762" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I762" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J762" s="14"/>
+      <c r="K762" s="14"/>
+      <c r="L762" s="14"/>
+      <c r="M762" s="14"/>
+      <c r="N762" s="14"/>
+      <c r="O762" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="P762" s="13" t="s">
+        <v>7689</v>
+      </c>
+      <c r="Q762" s="14"/>
+      <c r="R762" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S762" s="13" t="s">
+        <v>5590</v>
+      </c>
+      <c r="T762" s="14"/>
+      <c r="U762" s="14"/>
+      <c r="V762" s="14"/>
+      <c r="W762" s="14"/>
+      <c r="X762" s="14"/>
+      <c r="Y762" s="14"/>
+      <c r="Z762" s="14"/>
+      <c r="AA762" s="14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="763" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A763" s="13" t="s">
+        <v>7690</v>
+      </c>
+      <c r="B763" s="13" t="s">
+        <v>7691</v>
+      </c>
+      <c r="C763" s="13" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D763" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E763" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F763" s="14"/>
+      <c r="G763" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H763" s="13" t="s">
+        <v>7692</v>
+      </c>
+      <c r="I763" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J763" s="13" t="s">
+        <v>7693</v>
+      </c>
+      <c r="K763" s="14"/>
+      <c r="L763" s="14"/>
+      <c r="M763" s="14"/>
+      <c r="N763" s="14"/>
+      <c r="O763" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P763" s="13" t="s">
+        <v>7694</v>
+      </c>
+      <c r="Q763" s="14"/>
+      <c r="R763" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S763" s="13" t="s">
+        <v>5590</v>
+      </c>
+      <c r="T763" s="13" t="s">
+        <v>7695</v>
+      </c>
+      <c r="U763" s="14"/>
+      <c r="V763" s="14"/>
+      <c r="W763" s="14"/>
+      <c r="X763" s="14"/>
+      <c r="Y763" s="14"/>
+      <c r="Z763" s="13" t="s">
+        <v>3955</v>
+      </c>
+      <c r="AA763" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="764" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A764" s="13" t="s">
+        <v>7696</v>
+      </c>
+      <c r="B764" s="13" t="s">
+        <v>7697</v>
+      </c>
+      <c r="C764" s="13" t="s">
+        <v>7678</v>
+      </c>
+      <c r="D764" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E764" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F764" s="14"/>
+      <c r="G764" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H764" s="13" t="s">
+        <v>7698</v>
+      </c>
+      <c r="I764" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J764" s="13" t="s">
+        <v>7699</v>
+      </c>
+      <c r="K764" s="14"/>
+      <c r="L764" s="14"/>
+      <c r="M764" s="14"/>
+      <c r="N764" s="14"/>
+      <c r="O764" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P764" s="13" t="s">
+        <v>7700</v>
+      </c>
+      <c r="Q764" s="14"/>
+      <c r="R764" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S764" s="14"/>
+      <c r="T764" s="14"/>
+      <c r="U764" s="14"/>
+      <c r="V764" s="14"/>
+      <c r="W764" s="14"/>
+      <c r="X764" s="14"/>
+      <c r="Y764" s="14"/>
+      <c r="Z764" s="13" t="s">
+        <v>2157</v>
+      </c>
+      <c r="AA764" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="765" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A765" s="13" t="s">
+        <v>7701</v>
+      </c>
+      <c r="B765" s="13" t="s">
+        <v>7702</v>
+      </c>
+      <c r="C765" s="13" t="s">
+        <v>7703</v>
+      </c>
+      <c r="D765" s="14">
+        <v>2010</v>
+      </c>
+      <c r="E765" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F765" s="14"/>
+      <c r="G765" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H765" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I765" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J765" s="13" t="s">
+        <v>4439</v>
+      </c>
+      <c r="K765" s="14"/>
+      <c r="L765" s="14"/>
+      <c r="M765" s="14"/>
+      <c r="N765" s="14"/>
+      <c r="O765" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P765" s="13" t="s">
+        <v>7704</v>
+      </c>
+      <c r="Q765" s="14"/>
+      <c r="R765" s="14"/>
+      <c r="S765" s="13" t="s">
+        <v>2163</v>
+      </c>
+      <c r="T765" s="14"/>
+      <c r="U765" s="14"/>
+      <c r="V765" s="14"/>
+      <c r="W765" s="14"/>
+      <c r="X765" s="14"/>
+      <c r="Y765" s="14"/>
+      <c r="Z765" s="14"/>
+      <c r="AA765" s="14"/>
+    </row>
+    <row r="766" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A766" s="13" t="s">
+        <v>7705</v>
+      </c>
+      <c r="B766" s="13" t="s">
+        <v>7706</v>
+      </c>
+      <c r="C766" s="13" t="s">
+        <v>7678</v>
+      </c>
+      <c r="D766" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E766" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F766" s="14"/>
+      <c r="G766" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H766" s="13" t="s">
+        <v>7707</v>
+      </c>
+      <c r="I766" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J766" s="13" t="s">
+        <v>7708</v>
+      </c>
+      <c r="K766" s="14"/>
+      <c r="L766" s="14"/>
+      <c r="M766" s="14"/>
+      <c r="N766" s="14"/>
+      <c r="O766" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P766" s="13" t="s">
+        <v>6285</v>
+      </c>
+      <c r="Q766" s="14"/>
+      <c r="R766" s="14"/>
+      <c r="S766" s="14"/>
+      <c r="T766" s="14"/>
+      <c r="U766" s="14"/>
+      <c r="V766" s="14"/>
+      <c r="W766" s="14"/>
+      <c r="X766" s="14"/>
+      <c r="Y766" s="14"/>
+      <c r="Z766" s="14"/>
+      <c r="AA766" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="767" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A767" s="13" t="s">
+        <v>7709</v>
+      </c>
+      <c r="B767" s="13" t="s">
+        <v>7710</v>
+      </c>
+      <c r="C767" s="13" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D767" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E767" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F767" s="14"/>
+      <c r="G767" s="13" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H767" s="13" t="s">
+        <v>7711</v>
+      </c>
+      <c r="I767" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J767" s="14"/>
+      <c r="K767" s="14"/>
+      <c r="L767" s="14"/>
+      <c r="M767" s="14"/>
+      <c r="N767" s="14"/>
+      <c r="O767" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P767" s="13" t="s">
+        <v>7712</v>
+      </c>
+      <c r="Q767" s="14"/>
+      <c r="R767" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S767" s="13" t="s">
+        <v>5590</v>
+      </c>
+      <c r="T767" s="13" t="s">
+        <v>7713</v>
+      </c>
+      <c r="U767" s="14"/>
+      <c r="V767" s="14"/>
+      <c r="W767" s="13" t="s">
+        <v>7714</v>
+      </c>
+      <c r="X767" s="14"/>
+      <c r="Y767" s="14"/>
+      <c r="Z767" s="13" t="s">
+        <v>7715</v>
+      </c>
+      <c r="AA767" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="768" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A768" s="13" t="s">
+        <v>7716</v>
+      </c>
+      <c r="B768" s="13" t="s">
+        <v>7717</v>
+      </c>
+      <c r="C768" s="13" t="s">
+        <v>7718</v>
+      </c>
+      <c r="D768" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E768" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F768" s="14"/>
+      <c r="G768" s="13" t="s">
+        <v>4026</v>
+      </c>
+      <c r="H768" s="14"/>
+      <c r="I768" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J768" s="14"/>
+      <c r="K768" s="14"/>
+      <c r="L768" s="14"/>
+      <c r="M768" s="14"/>
+      <c r="N768" s="14"/>
+      <c r="O768" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P768" s="13" t="s">
+        <v>7719</v>
+      </c>
+      <c r="Q768" s="14"/>
+      <c r="R768" s="14"/>
+      <c r="S768" s="13" t="s">
+        <v>7720</v>
+      </c>
+      <c r="T768" s="14"/>
+      <c r="U768" s="14"/>
+      <c r="V768" s="14"/>
+      <c r="W768" s="14"/>
+      <c r="X768" s="14"/>
+      <c r="Y768" s="14"/>
+      <c r="Z768" s="13" t="s">
+        <v>7721</v>
+      </c>
+      <c r="AA768" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="769" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A769" s="13" t="s">
+        <v>7722</v>
+      </c>
+      <c r="B769" s="13" t="s">
+        <v>7723</v>
+      </c>
+      <c r="C769" s="13" t="s">
+        <v>5572</v>
+      </c>
+      <c r="D769" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E769" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F769" s="14"/>
+      <c r="G769" s="13" t="s">
+        <v>7724</v>
+      </c>
+      <c r="H769" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="I769" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J769" s="14"/>
+      <c r="K769" s="14"/>
+      <c r="L769" s="14"/>
+      <c r="M769" s="14"/>
+      <c r="N769" s="14"/>
+      <c r="O769" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="P769" s="13" t="s">
+        <v>7725</v>
+      </c>
+      <c r="Q769" s="14"/>
+      <c r="R769" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S769" s="13" t="s">
+        <v>5577</v>
+      </c>
+      <c r="T769" s="13" t="s">
+        <v>7726</v>
+      </c>
+      <c r="U769" s="14"/>
+      <c r="V769" s="14"/>
+      <c r="W769" s="14"/>
+      <c r="X769" s="14"/>
+      <c r="Y769" s="14"/>
+      <c r="Z769" s="13" t="s">
+        <v>7727</v>
+      </c>
+      <c r="AA769" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="770" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A770" s="13" t="s">
+        <v>7728</v>
+      </c>
+      <c r="B770" s="13" t="s">
+        <v>7729</v>
+      </c>
+      <c r="C770" s="13" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D770" s="14">
+        <v>2014</v>
+      </c>
+      <c r="E770" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F770" s="14"/>
+      <c r="G770" s="13" t="s">
+        <v>6130</v>
+      </c>
+      <c r="H770" s="13" t="s">
+        <v>7731</v>
+      </c>
+      <c r="I770" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J770" s="13" t="s">
+        <v>7732</v>
+      </c>
+      <c r="K770" s="14"/>
+      <c r="L770" s="14"/>
+      <c r="M770" s="14"/>
+      <c r="N770" s="14"/>
+      <c r="O770" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P770" s="13" t="s">
+        <v>7733</v>
+      </c>
+      <c r="Q770" s="14"/>
+      <c r="R770" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S770" s="13" t="s">
+        <v>7734</v>
+      </c>
+      <c r="T770" s="13" t="s">
+        <v>7735</v>
+      </c>
+      <c r="U770" s="14"/>
+      <c r="V770" s="14"/>
+      <c r="W770" s="14"/>
+      <c r="X770" s="14"/>
+      <c r="Y770" s="14"/>
+      <c r="Z770" s="13" t="s">
+        <v>7736</v>
+      </c>
+      <c r="AA770" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="771" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A771" s="13" t="s">
+        <v>7737</v>
+      </c>
+      <c r="B771" s="13" t="s">
+        <v>7738</v>
+      </c>
+      <c r="C771" s="13" t="s">
+        <v>7739</v>
+      </c>
+      <c r="D771" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E771" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F771" s="14"/>
+      <c r="G771" s="13" t="s">
+        <v>2308</v>
+      </c>
+      <c r="H771" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I771" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J771" s="14"/>
+      <c r="K771" s="14"/>
+      <c r="L771" s="14"/>
+      <c r="M771" s="14"/>
+      <c r="N771" s="14"/>
+      <c r="O771" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P771" s="13" t="s">
+        <v>7740</v>
+      </c>
+      <c r="Q771" s="14"/>
+      <c r="R771" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S771" s="14"/>
+      <c r="T771" s="13" t="s">
+        <v>7741</v>
+      </c>
+      <c r="U771" s="13" t="s">
+        <v>7742</v>
+      </c>
+      <c r="V771" s="14"/>
+      <c r="W771" s="14"/>
+      <c r="X771" s="14"/>
+      <c r="Y771" s="14"/>
+      <c r="Z771" s="13" t="s">
+        <v>6008</v>
+      </c>
+      <c r="AA771" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="772" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A772" s="13" t="s">
+        <v>7743</v>
+      </c>
+      <c r="B772" s="13" t="s">
+        <v>7744</v>
+      </c>
+      <c r="C772" s="13" t="s">
+        <v>7745</v>
+      </c>
+      <c r="D772" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E772" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F772" s="14"/>
+      <c r="G772" s="13" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H772" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="I772" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J772" s="13" t="s">
+        <v>7746</v>
+      </c>
+      <c r="K772" s="14"/>
+      <c r="L772" s="14"/>
+      <c r="M772" s="14"/>
+      <c r="N772" s="14"/>
+      <c r="O772" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P772" s="13" t="s">
+        <v>6285</v>
+      </c>
+      <c r="Q772" s="14"/>
+      <c r="R772" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S772" s="13" t="s">
+        <v>5590</v>
+      </c>
+      <c r="T772" s="13" t="s">
+        <v>7747</v>
+      </c>
+      <c r="U772" s="14"/>
+      <c r="V772" s="14"/>
+      <c r="W772" s="14"/>
+      <c r="X772" s="14"/>
+      <c r="Y772" s="14"/>
+      <c r="Z772" s="13" t="s">
+        <v>1206</v>
+      </c>
+      <c r="AA772" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="773" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A773" s="13" t="s">
+        <v>7748</v>
+      </c>
+      <c r="B773" s="13" t="s">
+        <v>7749</v>
+      </c>
+      <c r="C773" s="13" t="s">
+        <v>6142</v>
+      </c>
+      <c r="D773" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E773" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F773" s="14"/>
+      <c r="G773" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H773" s="13" t="s">
+        <v>3294</v>
+      </c>
+      <c r="I773" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J773" s="13" t="s">
+        <v>7750</v>
+      </c>
+      <c r="K773" s="14"/>
+      <c r="L773" s="14"/>
+      <c r="M773" s="14"/>
+      <c r="N773" s="14"/>
+      <c r="O773" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P773" s="13" t="s">
+        <v>7751</v>
+      </c>
+      <c r="Q773" s="14"/>
+      <c r="R773" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S773" s="13" t="s">
+        <v>7752</v>
+      </c>
+      <c r="T773" s="13" t="s">
+        <v>7753</v>
+      </c>
+      <c r="U773" s="14"/>
+      <c r="V773" s="14"/>
+      <c r="W773" s="14"/>
+      <c r="X773" s="14"/>
+      <c r="Y773" s="14"/>
+      <c r="Z773" s="13" t="s">
+        <v>7754</v>
+      </c>
+      <c r="AA773" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="774" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A774" s="13" t="s">
+        <v>7755</v>
+      </c>
+      <c r="B774" s="13" t="s">
+        <v>7756</v>
+      </c>
+      <c r="C774" s="13" t="s">
+        <v>7745</v>
+      </c>
+      <c r="D774" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E774" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F774" s="14"/>
+      <c r="G774" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H774" s="13" t="s">
+        <v>3294</v>
+      </c>
+      <c r="I774" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J774" s="13" t="s">
+        <v>4376</v>
+      </c>
+      <c r="K774" s="14"/>
+      <c r="L774" s="14"/>
+      <c r="M774" s="14"/>
+      <c r="N774" s="14"/>
+      <c r="O774" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P774" s="13" t="s">
+        <v>7757</v>
+      </c>
+      <c r="Q774" s="14"/>
+      <c r="R774" s="14"/>
+      <c r="S774" s="14"/>
+      <c r="T774" s="14"/>
+      <c r="U774" s="14"/>
+      <c r="V774" s="14"/>
+      <c r="W774" s="14"/>
+      <c r="X774" s="14"/>
+      <c r="Y774" s="14"/>
+      <c r="Z774" s="14"/>
+      <c r="AA774" s="14"/>
+    </row>
+    <row r="775" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A775" s="13" t="s">
+        <v>7758</v>
+      </c>
+      <c r="B775" s="13" t="s">
+        <v>7759</v>
+      </c>
+      <c r="C775" s="13" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D775" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E775" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F775" s="14"/>
+      <c r="G775" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H775" s="13" t="s">
+        <v>7760</v>
+      </c>
+      <c r="I775" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J775" s="13" t="s">
+        <v>7761</v>
+      </c>
+      <c r="K775" s="14"/>
+      <c r="L775" s="14"/>
+      <c r="M775" s="14"/>
+      <c r="N775" s="14"/>
+      <c r="O775" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P775" s="13" t="s">
+        <v>5698</v>
+      </c>
+      <c r="Q775" s="14"/>
+      <c r="R775" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S775" s="13" t="s">
+        <v>7762</v>
+      </c>
+      <c r="T775" s="14"/>
+      <c r="U775" s="14"/>
+      <c r="V775" s="14"/>
+      <c r="W775" s="14"/>
+      <c r="X775" s="14"/>
+      <c r="Y775" s="14"/>
+      <c r="Z775" s="13" t="s">
+        <v>7763</v>
+      </c>
+      <c r="AA775" s="14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="776" spans="1:27" ht="90" x14ac:dyDescent="0.25">
+      <c r="A776" s="13" t="s">
+        <v>7764</v>
+      </c>
+      <c r="B776" s="13" t="s">
+        <v>7765</v>
+      </c>
+      <c r="C776" s="13" t="s">
+        <v>7766</v>
+      </c>
+      <c r="D776" s="14">
+        <v>2012</v>
+      </c>
+      <c r="E776" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F776" s="14"/>
+      <c r="G776" s="13" t="s">
+        <v>7767</v>
+      </c>
+      <c r="H776" s="13" t="s">
+        <v>2174</v>
+      </c>
+      <c r="I776" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J776" s="13" t="s">
+        <v>7768</v>
+      </c>
+      <c r="K776" s="14"/>
+      <c r="L776" s="14"/>
+      <c r="M776" s="14"/>
+      <c r="N776" s="14"/>
+      <c r="O776" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P776" s="13" t="s">
+        <v>7769</v>
+      </c>
+      <c r="Q776" s="14"/>
+      <c r="R776" s="13" t="s">
+        <v>5457</v>
+      </c>
+      <c r="S776" s="13" t="s">
+        <v>7770</v>
+      </c>
+      <c r="T776" s="13" t="s">
+        <v>7771</v>
+      </c>
+      <c r="U776" s="13" t="s">
+        <v>7772</v>
+      </c>
+      <c r="V776" s="14"/>
+      <c r="W776" s="14"/>
+      <c r="X776" s="14"/>
+      <c r="Y776" s="14"/>
+      <c r="Z776" s="13" t="s">
+        <v>7773</v>
+      </c>
+      <c r="AA776" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="777" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A777" s="13" t="s">
+        <v>7774</v>
+      </c>
+      <c r="B777" s="13" t="s">
+        <v>7775</v>
+      </c>
+      <c r="C777" s="13" t="s">
+        <v>7776</v>
+      </c>
+      <c r="D777" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E777" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F777" s="14"/>
+      <c r="G777" s="13" t="s">
+        <v>7777</v>
+      </c>
+      <c r="H777" s="13" t="s">
+        <v>7778</v>
+      </c>
+      <c r="I777" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J777" s="13" t="s">
+        <v>7779</v>
+      </c>
+      <c r="K777" s="14"/>
+      <c r="L777" s="14"/>
+      <c r="M777" s="14"/>
+      <c r="N777" s="14"/>
+      <c r="O777" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P777" s="13" t="s">
+        <v>7780</v>
+      </c>
+      <c r="Q777" s="14"/>
+      <c r="R777" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S777" s="13" t="s">
+        <v>7781</v>
+      </c>
+      <c r="T777" s="13" t="s">
+        <v>7782</v>
+      </c>
+      <c r="U777" s="14"/>
+      <c r="V777" s="14"/>
+      <c r="W777" s="14"/>
+      <c r="X777" s="14"/>
+      <c r="Y777" s="14"/>
+      <c r="Z777" s="13" t="s">
+        <v>7783</v>
+      </c>
+      <c r="AA777" s="14">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="778" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A778" s="13" t="s">
+        <v>7784</v>
+      </c>
+      <c r="B778" s="13" t="s">
+        <v>7785</v>
+      </c>
+      <c r="C778" s="13" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D778" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E778" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F778" s="14"/>
+      <c r="G778" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H778" s="13" t="s">
+        <v>7786</v>
+      </c>
+      <c r="I778" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J778" s="13" t="s">
+        <v>7787</v>
+      </c>
+      <c r="K778" s="14"/>
+      <c r="L778" s="14"/>
+      <c r="M778" s="14"/>
+      <c r="N778" s="14"/>
+      <c r="O778" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P778" s="13" t="s">
+        <v>7788</v>
+      </c>
+      <c r="Q778" s="14"/>
+      <c r="R778" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S778" s="14"/>
+      <c r="T778" s="13" t="s">
+        <v>7789</v>
+      </c>
+      <c r="U778" s="14"/>
+      <c r="V778" s="14"/>
+      <c r="W778" s="14"/>
+      <c r="X778" s="14"/>
+      <c r="Y778" s="14"/>
+      <c r="Z778" s="13" t="s">
+        <v>7790</v>
+      </c>
+      <c r="AA778" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="779" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A779" s="13" t="s">
+        <v>7791</v>
+      </c>
+      <c r="B779" s="13" t="s">
+        <v>7792</v>
+      </c>
+      <c r="C779" s="13" t="s">
+        <v>7776</v>
+      </c>
+      <c r="D779" s="14">
+        <v>2013</v>
+      </c>
+      <c r="E779" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F779" s="14"/>
+      <c r="G779" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H779" s="13" t="s">
+        <v>1516</v>
+      </c>
+      <c r="I779" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J779" s="14"/>
+      <c r="K779" s="14"/>
+      <c r="L779" s="14"/>
+      <c r="M779" s="14"/>
+      <c r="N779" s="14"/>
+      <c r="O779" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P779" s="13" t="s">
+        <v>7793</v>
+      </c>
+      <c r="Q779" s="14"/>
+      <c r="R779" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S779" s="13" t="s">
+        <v>7794</v>
+      </c>
+      <c r="T779" s="13" t="s">
+        <v>7795</v>
+      </c>
+      <c r="U779" s="14"/>
+      <c r="V779" s="14"/>
+      <c r="W779" s="14"/>
+      <c r="X779" s="14"/>
+      <c r="Y779" s="14"/>
+      <c r="Z779" s="13" t="s">
+        <v>7796</v>
+      </c>
+      <c r="AA779" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="780" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A780" s="13" t="s">
+        <v>7797</v>
+      </c>
+      <c r="B780" s="13" t="s">
+        <v>7798</v>
+      </c>
+      <c r="C780" s="13" t="s">
+        <v>7799</v>
+      </c>
+      <c r="D780" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E780" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F780" s="14"/>
+      <c r="G780" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H780" s="14"/>
+      <c r="I780" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J780" s="14"/>
+      <c r="K780" s="14"/>
+      <c r="L780" s="14"/>
+      <c r="M780" s="14"/>
+      <c r="N780" s="14"/>
+      <c r="O780" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P780" s="13" t="s">
+        <v>7800</v>
+      </c>
+      <c r="Q780" s="14"/>
+      <c r="R780" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S780" s="13" t="s">
+        <v>7801</v>
+      </c>
+      <c r="T780" s="13" t="s">
+        <v>7802</v>
+      </c>
+      <c r="U780" s="13" t="s">
+        <v>7803</v>
+      </c>
+      <c r="V780" s="14"/>
+      <c r="W780" s="13" t="s">
+        <v>7804</v>
+      </c>
+      <c r="X780" s="13" t="s">
+        <v>7805</v>
+      </c>
+      <c r="Y780" s="13" t="s">
+        <v>7806</v>
+      </c>
+      <c r="Z780" s="13" t="s">
+        <v>1457</v>
+      </c>
+      <c r="AA780" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="781" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A781" s="13" t="s">
+        <v>7807</v>
+      </c>
+      <c r="B781" s="13" t="s">
+        <v>7808</v>
+      </c>
+      <c r="C781" s="13" t="s">
+        <v>7739</v>
+      </c>
+      <c r="D781" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E781" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F781" s="14"/>
+      <c r="G781" s="13" t="s">
+        <v>4164</v>
+      </c>
+      <c r="H781" s="13" t="s">
+        <v>3005</v>
+      </c>
+      <c r="I781" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J781" s="14"/>
+      <c r="K781" s="14"/>
+      <c r="L781" s="14"/>
+      <c r="M781" s="14"/>
+      <c r="N781" s="14"/>
+      <c r="O781" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P781" s="13" t="s">
+        <v>7809</v>
+      </c>
+      <c r="Q781" s="14"/>
+      <c r="R781" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S781" s="14"/>
+      <c r="T781" s="13" t="s">
+        <v>7810</v>
+      </c>
+      <c r="U781" s="14"/>
+      <c r="V781" s="14"/>
+      <c r="W781" s="14"/>
+      <c r="X781" s="14"/>
+      <c r="Y781" s="14"/>
+      <c r="Z781" s="13" t="s">
+        <v>7811</v>
+      </c>
+      <c r="AA781" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="782" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A782" s="13" t="s">
+        <v>7812</v>
+      </c>
+      <c r="B782" s="13" t="s">
+        <v>7813</v>
+      </c>
+      <c r="C782" s="13" t="s">
+        <v>6079</v>
+      </c>
+      <c r="D782" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E782" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F782" s="14"/>
+      <c r="G782" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="H782" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="I782" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J782" s="13" t="s">
+        <v>7814</v>
+      </c>
+      <c r="K782" s="14"/>
+      <c r="L782" s="14"/>
+      <c r="M782" s="14"/>
+      <c r="N782" s="14"/>
+      <c r="O782" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P782" s="13" t="s">
+        <v>7815</v>
+      </c>
+      <c r="Q782" s="14"/>
+      <c r="R782" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S782" s="14"/>
+      <c r="T782" s="14"/>
+      <c r="U782" s="14"/>
+      <c r="V782" s="14"/>
+      <c r="W782" s="14"/>
+      <c r="X782" s="14"/>
+      <c r="Y782" s="14"/>
+      <c r="Z782" s="13" t="s">
+        <v>7816</v>
+      </c>
+      <c r="AA782" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="783" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A783" s="13" t="s">
+        <v>7817</v>
+      </c>
+      <c r="B783" s="13" t="s">
+        <v>7818</v>
+      </c>
+      <c r="C783" s="13" t="s">
+        <v>7739</v>
+      </c>
+      <c r="D783" s="14">
+        <v>2012</v>
+      </c>
+      <c r="E783" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F783" s="14"/>
+      <c r="G783" s="13" t="s">
+        <v>2371</v>
+      </c>
+      <c r="H783" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I783" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J783" s="13" t="s">
+        <v>7819</v>
+      </c>
+      <c r="K783" s="14"/>
+      <c r="L783" s="14"/>
+      <c r="M783" s="14"/>
+      <c r="N783" s="14"/>
+      <c r="O783" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="P783" s="13" t="s">
+        <v>7820</v>
+      </c>
+      <c r="Q783" s="14"/>
+      <c r="R783" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S783" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="T783" s="13" t="s">
+        <v>7821</v>
+      </c>
+      <c r="U783" s="14"/>
+      <c r="V783" s="14"/>
+      <c r="W783" s="14"/>
+      <c r="X783" s="14"/>
+      <c r="Y783" s="14"/>
+      <c r="Z783" s="13" t="s">
+        <v>7822</v>
+      </c>
+      <c r="AA783" s="14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="784" spans="1:27" ht="105" x14ac:dyDescent="0.25">
+      <c r="A784" s="13" t="s">
+        <v>7823</v>
+      </c>
+      <c r="B784" s="13" t="s">
+        <v>7824</v>
+      </c>
+      <c r="C784" s="13" t="s">
+        <v>7825</v>
+      </c>
+      <c r="D784" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E784" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F784" s="14"/>
+      <c r="G784" s="13" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H784" s="13" t="s">
+        <v>2250</v>
+      </c>
+      <c r="I784" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J784" s="13" t="s">
+        <v>7826</v>
+      </c>
+      <c r="K784" s="14"/>
+      <c r="L784" s="14"/>
+      <c r="M784" s="14"/>
+      <c r="N784" s="14"/>
+      <c r="O784" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="P784" s="13" t="s">
+        <v>7827</v>
+      </c>
+      <c r="Q784" s="14"/>
+      <c r="R784" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S784" s="14"/>
+      <c r="T784" s="13" t="s">
+        <v>7828</v>
+      </c>
+      <c r="U784" s="14"/>
+      <c r="V784" s="13" t="s">
+        <v>7829</v>
+      </c>
+      <c r="W784" s="14"/>
+      <c r="X784" s="14"/>
+      <c r="Y784" s="13" t="s">
+        <v>7830</v>
+      </c>
+      <c r="Z784" s="14"/>
+      <c r="AA784" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="785" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A785" s="13" t="s">
+        <v>7831</v>
+      </c>
+      <c r="B785" s="13" t="s">
+        <v>7832</v>
+      </c>
+      <c r="C785" s="13" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D785" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E785" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F785" s="14"/>
+      <c r="G785" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H785" s="13" t="s">
+        <v>7833</v>
+      </c>
+      <c r="I785" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J785" s="14"/>
+      <c r="K785" s="14"/>
+      <c r="L785" s="14"/>
+      <c r="M785" s="14"/>
+      <c r="N785" s="14"/>
+      <c r="O785" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P785" s="13" t="s">
+        <v>7834</v>
+      </c>
+      <c r="Q785" s="14"/>
+      <c r="R785" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S785" s="13" t="s">
+        <v>7762</v>
+      </c>
+      <c r="T785" s="13" t="s">
+        <v>7835</v>
+      </c>
+      <c r="U785" s="14"/>
+      <c r="V785" s="14"/>
+      <c r="W785" s="14"/>
+      <c r="X785" s="14"/>
+      <c r="Y785" s="14"/>
+      <c r="Z785" s="14"/>
+      <c r="AA785" s="14">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="786" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A786" s="13" t="s">
+        <v>7836</v>
+      </c>
+      <c r="B786" s="13" t="s">
+        <v>7837</v>
+      </c>
+      <c r="C786" s="13" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D786" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E786" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F786" s="14"/>
+      <c r="G786" s="13" t="s">
+        <v>7838</v>
+      </c>
+      <c r="H786" s="13" t="s">
+        <v>7839</v>
+      </c>
+      <c r="I786" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J786" s="13" t="s">
+        <v>4439</v>
+      </c>
+      <c r="K786" s="14"/>
+      <c r="L786" s="14"/>
+      <c r="M786" s="14"/>
+      <c r="N786" s="14"/>
+      <c r="O786" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P786" s="13" t="s">
+        <v>6418</v>
+      </c>
+      <c r="Q786" s="14"/>
+      <c r="R786" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S786" s="13" t="s">
+        <v>7762</v>
+      </c>
+      <c r="T786" s="14"/>
+      <c r="U786" s="14"/>
+      <c r="V786" s="14"/>
+      <c r="W786" s="14"/>
+      <c r="X786" s="14"/>
+      <c r="Y786" s="14"/>
+      <c r="Z786" s="13" t="s">
+        <v>7840</v>
+      </c>
+      <c r="AA786" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="787" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A787" s="13" t="s">
+        <v>7841</v>
+      </c>
+      <c r="B787" s="13" t="s">
+        <v>7842</v>
+      </c>
+      <c r="C787" s="13" t="s">
+        <v>7843</v>
+      </c>
+      <c r="D787" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E787" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F787" s="14"/>
+      <c r="G787" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H787" s="13" t="s">
+        <v>7711</v>
+      </c>
+      <c r="I787" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J787" s="13" t="s">
+        <v>7844</v>
+      </c>
+      <c r="K787" s="14"/>
+      <c r="L787" s="14"/>
+      <c r="M787" s="14"/>
+      <c r="N787" s="14"/>
+      <c r="O787" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P787" s="13" t="s">
+        <v>7845</v>
+      </c>
+      <c r="Q787" s="13" t="s">
+        <v>2205</v>
+      </c>
+      <c r="R787" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S787" s="14"/>
+      <c r="T787" s="13" t="s">
+        <v>7846</v>
+      </c>
+      <c r="U787" s="14"/>
+      <c r="V787" s="14"/>
+      <c r="W787" s="14"/>
+      <c r="X787" s="14"/>
+      <c r="Y787" s="14"/>
+      <c r="Z787" s="14"/>
+      <c r="AA787" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="788" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A788" s="13" t="s">
+        <v>7847</v>
+      </c>
+      <c r="B788" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C788" s="13" t="s">
+        <v>7848</v>
+      </c>
+      <c r="D788" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E788" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F788" s="14"/>
+      <c r="G788" s="13" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H788" s="14"/>
+      <c r="I788" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J788" s="14"/>
+      <c r="K788" s="14"/>
+      <c r="L788" s="14"/>
+      <c r="M788" s="14"/>
+      <c r="N788" s="14"/>
+      <c r="O788" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P788" s="13" t="s">
+        <v>6372</v>
+      </c>
+      <c r="Q788" s="14"/>
+      <c r="R788" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S788" s="14"/>
+      <c r="T788" s="14"/>
+      <c r="U788" s="14"/>
+      <c r="V788" s="14"/>
+      <c r="W788" s="14"/>
+      <c r="X788" s="14"/>
+      <c r="Y788" s="14"/>
+      <c r="Z788" s="13" t="s">
+        <v>4447</v>
+      </c>
+      <c r="AA788" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="789" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A789" s="13" t="s">
+        <v>7849</v>
+      </c>
+      <c r="B789" s="13" t="s">
+        <v>7850</v>
+      </c>
+      <c r="C789" s="13" t="s">
+        <v>7851</v>
+      </c>
+      <c r="D789" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E789" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F789" s="14"/>
+      <c r="G789" s="13" t="s">
+        <v>7852</v>
+      </c>
+      <c r="H789" s="14"/>
+      <c r="I789" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J789" s="13" t="s">
+        <v>7853</v>
+      </c>
+      <c r="K789" s="14"/>
+      <c r="L789" s="14"/>
+      <c r="M789" s="14"/>
+      <c r="N789" s="14"/>
+      <c r="O789" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P789" s="13" t="s">
+        <v>7694</v>
+      </c>
+      <c r="Q789" s="14"/>
+      <c r="R789" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S789" s="14"/>
+      <c r="T789" s="13" t="s">
+        <v>7854</v>
+      </c>
+      <c r="U789" s="14"/>
+      <c r="V789" s="14"/>
+      <c r="W789" s="14"/>
+      <c r="X789" s="14"/>
+      <c r="Y789" s="14"/>
+      <c r="Z789" s="13" t="s">
+        <v>7855</v>
+      </c>
+      <c r="AA789" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="790" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A790" s="13" t="s">
+        <v>7856</v>
+      </c>
+      <c r="B790" s="13" t="s">
+        <v>7857</v>
+      </c>
+      <c r="C790" s="13" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D790" s="14">
+        <v>2012</v>
+      </c>
+      <c r="E790" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F790" s="14"/>
+      <c r="G790" s="13" t="s">
+        <v>605</v>
+      </c>
+      <c r="H790" s="13" t="s">
+        <v>2333</v>
+      </c>
+      <c r="I790" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J790" s="13" t="s">
+        <v>7858</v>
+      </c>
+      <c r="K790" s="14"/>
+      <c r="L790" s="14"/>
+      <c r="M790" s="14"/>
+      <c r="N790" s="14"/>
+      <c r="O790" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P790" s="13" t="s">
+        <v>7859</v>
+      </c>
+      <c r="Q790" s="14"/>
+      <c r="R790" s="14"/>
+      <c r="S790" s="13" t="s">
+        <v>899</v>
+      </c>
+      <c r="T790" s="14"/>
+      <c r="U790" s="14"/>
+      <c r="V790" s="14"/>
+      <c r="W790" s="14"/>
+      <c r="X790" s="14"/>
+      <c r="Y790" s="14"/>
+      <c r="Z790" s="13" t="s">
+        <v>7178</v>
+      </c>
+      <c r="AA790" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="791" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A791" s="13" t="s">
+        <v>7860</v>
+      </c>
+      <c r="B791" s="13" t="s">
+        <v>7861</v>
+      </c>
+      <c r="C791" s="13" t="s">
+        <v>7799</v>
+      </c>
+      <c r="D791" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E791" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F791" s="14"/>
+      <c r="G791" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H791" s="13" t="s">
+        <v>7862</v>
+      </c>
+      <c r="I791" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J791" s="14"/>
+      <c r="K791" s="14"/>
+      <c r="L791" s="14"/>
+      <c r="M791" s="14"/>
+      <c r="N791" s="14"/>
+      <c r="O791" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P791" s="13" t="s">
+        <v>7863</v>
+      </c>
+      <c r="Q791" s="14"/>
+      <c r="R791" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S791" s="13" t="s">
+        <v>7801</v>
+      </c>
+      <c r="T791" s="13" t="s">
+        <v>7864</v>
+      </c>
+      <c r="U791" s="14"/>
+      <c r="V791" s="14"/>
+      <c r="W791" s="14"/>
+      <c r="X791" s="14"/>
+      <c r="Y791" s="14"/>
+      <c r="Z791" s="13" t="s">
+        <v>6871</v>
+      </c>
+      <c r="AA791" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="792" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A792" s="13" t="s">
+        <v>7865</v>
+      </c>
+      <c r="B792" s="13" t="s">
+        <v>7866</v>
+      </c>
+      <c r="C792" s="13" t="s">
+        <v>7867</v>
+      </c>
+      <c r="D792" s="14">
+        <v>2014</v>
+      </c>
+      <c r="E792" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F792" s="14"/>
+      <c r="G792" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H792" s="13" t="s">
+        <v>7868</v>
+      </c>
+      <c r="I792" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J792" s="14"/>
+      <c r="K792" s="14"/>
+      <c r="L792" s="14"/>
+      <c r="M792" s="14"/>
+      <c r="N792" s="14"/>
+      <c r="O792" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P792" s="13" t="s">
+        <v>7869</v>
+      </c>
+      <c r="Q792" s="14"/>
+      <c r="R792" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S792" s="13" t="s">
+        <v>7794</v>
+      </c>
+      <c r="T792" s="13" t="s">
+        <v>7870</v>
+      </c>
+      <c r="U792" s="14"/>
+      <c r="V792" s="14"/>
+      <c r="W792" s="14"/>
+      <c r="X792" s="14"/>
+      <c r="Y792" s="14"/>
+      <c r="Z792" s="13" t="s">
+        <v>7871</v>
+      </c>
+      <c r="AA792" s="14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="793" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A793" s="13" t="s">
+        <v>7872</v>
+      </c>
+      <c r="B793" s="13" t="s">
+        <v>7873</v>
+      </c>
+      <c r="C793" s="13" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D793" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E793" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F793" s="14"/>
+      <c r="G793" s="13" t="s">
+        <v>7862</v>
+      </c>
+      <c r="H793" s="14"/>
+      <c r="I793" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J793" s="14"/>
+      <c r="K793" s="14"/>
+      <c r="L793" s="14"/>
+      <c r="M793" s="14"/>
+      <c r="N793" s="14"/>
+      <c r="O793" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P793" s="13" t="s">
+        <v>6219</v>
+      </c>
+      <c r="Q793" s="14"/>
+      <c r="R793" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S793" s="13" t="s">
+        <v>7762</v>
+      </c>
+      <c r="T793" s="13" t="s">
+        <v>7874</v>
+      </c>
+      <c r="U793" s="14"/>
+      <c r="V793" s="14"/>
+      <c r="W793" s="14"/>
+      <c r="X793" s="14"/>
+      <c r="Y793" s="14"/>
+      <c r="Z793" s="14"/>
+      <c r="AA793" s="14">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="794" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A794" s="13" t="s">
+        <v>7875</v>
+      </c>
+      <c r="B794" s="13" t="s">
+        <v>7876</v>
+      </c>
+      <c r="C794" s="13" t="s">
+        <v>7877</v>
+      </c>
+      <c r="D794" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E794" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F794" s="14"/>
+      <c r="G794" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H794" s="13" t="s">
+        <v>6130</v>
+      </c>
+      <c r="I794" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J794" s="13" t="s">
+        <v>7878</v>
+      </c>
+      <c r="K794" s="14"/>
+      <c r="L794" s="14"/>
+      <c r="M794" s="14"/>
+      <c r="N794" s="14"/>
+      <c r="O794" s="13" t="s">
+        <v>3406</v>
+      </c>
+      <c r="P794" s="13" t="s">
+        <v>7879</v>
+      </c>
+      <c r="Q794" s="14"/>
+      <c r="R794" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S794" s="13" t="s">
+        <v>6470</v>
+      </c>
+      <c r="T794" s="14"/>
+      <c r="U794" s="14"/>
+      <c r="V794" s="14"/>
+      <c r="W794" s="14"/>
+      <c r="X794" s="14"/>
+      <c r="Y794" s="14"/>
+      <c r="Z794" s="13" t="s">
+        <v>7880</v>
+      </c>
+      <c r="AA794" s="14">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="795" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A795" s="13" t="s">
+        <v>7881</v>
+      </c>
+      <c r="B795" s="13" t="s">
+        <v>7882</v>
+      </c>
+      <c r="C795" s="13" t="s">
+        <v>5627</v>
+      </c>
+      <c r="D795" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E795" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F795" s="14"/>
+      <c r="G795" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H795" s="13" t="s">
+        <v>3687</v>
+      </c>
+      <c r="I795" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J795" s="14"/>
+      <c r="K795" s="14"/>
+      <c r="L795" s="14"/>
+      <c r="M795" s="14"/>
+      <c r="N795" s="14"/>
+      <c r="O795" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="P795" s="13" t="s">
+        <v>7883</v>
+      </c>
+      <c r="Q795" s="14"/>
+      <c r="R795" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S795" s="14"/>
+      <c r="T795" s="14"/>
+      <c r="U795" s="13" t="s">
+        <v>7884</v>
+      </c>
+      <c r="V795" s="14"/>
+      <c r="W795" s="14"/>
+      <c r="X795" s="14"/>
+      <c r="Y795" s="14"/>
+      <c r="Z795" s="13" t="s">
+        <v>7885</v>
+      </c>
+      <c r="AA795" s="14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="796" spans="1:27" ht="90" x14ac:dyDescent="0.25">
+      <c r="A796" s="13" t="s">
+        <v>7886</v>
+      </c>
+      <c r="B796" s="13" t="s">
+        <v>7887</v>
+      </c>
+      <c r="C796" s="13" t="s">
+        <v>7730</v>
+      </c>
+      <c r="D796" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E796" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F796" s="14"/>
+      <c r="G796" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H796" s="13" t="s">
+        <v>7888</v>
+      </c>
+      <c r="I796" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J796" s="14"/>
+      <c r="K796" s="14"/>
+      <c r="L796" s="14"/>
+      <c r="M796" s="14"/>
+      <c r="N796" s="14"/>
+      <c r="O796" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P796" s="13" t="s">
+        <v>6026</v>
+      </c>
+      <c r="Q796" s="14"/>
+      <c r="R796" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S796" s="13" t="s">
+        <v>7762</v>
+      </c>
+      <c r="T796" s="13" t="s">
+        <v>7889</v>
+      </c>
+      <c r="U796" s="14"/>
+      <c r="V796" s="14"/>
+      <c r="W796" s="14"/>
+      <c r="X796" s="14"/>
+      <c r="Y796" s="14"/>
+      <c r="Z796" s="14"/>
+      <c r="AA796" s="14">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="797" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A797" s="13" t="s">
+        <v>7890</v>
+      </c>
+      <c r="B797" s="13" t="s">
+        <v>7891</v>
+      </c>
+      <c r="C797" s="13" t="s">
+        <v>6318</v>
+      </c>
+      <c r="D797" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E797" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F797" s="14"/>
+      <c r="G797" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H797" s="13" t="s">
+        <v>772</v>
+      </c>
+      <c r="I797" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J797" s="14"/>
+      <c r="K797" s="14"/>
+      <c r="L797" s="14"/>
+      <c r="M797" s="14"/>
+      <c r="N797" s="14"/>
+      <c r="O797" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P797" s="13" t="s">
+        <v>3466</v>
+      </c>
+      <c r="Q797" s="14"/>
+      <c r="R797" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S797" s="14"/>
+      <c r="T797" s="14"/>
+      <c r="U797" s="13" t="s">
+        <v>7892</v>
+      </c>
+      <c r="V797" s="14"/>
+      <c r="W797" s="14"/>
+      <c r="X797" s="14"/>
+      <c r="Y797" s="14"/>
+      <c r="Z797" s="13" t="s">
+        <v>7893</v>
+      </c>
+      <c r="AA797" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="798" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A798" s="13" t="s">
+        <v>7894</v>
+      </c>
+      <c r="B798" s="13" t="s">
+        <v>7895</v>
+      </c>
+      <c r="C798" s="13" t="s">
+        <v>6253</v>
+      </c>
+      <c r="D798" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E798" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F798" s="14"/>
+      <c r="G798" s="13" t="s">
+        <v>4106</v>
+      </c>
+      <c r="H798" s="14"/>
+      <c r="I798" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J798" s="13" t="s">
+        <v>7896</v>
+      </c>
+      <c r="K798" s="14"/>
+      <c r="L798" s="14"/>
+      <c r="M798" s="14"/>
+      <c r="N798" s="14"/>
+      <c r="O798" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P798" s="13" t="s">
+        <v>7897</v>
+      </c>
+      <c r="Q798" s="14"/>
+      <c r="R798" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S798" s="13" t="s">
+        <v>7898</v>
+      </c>
+      <c r="T798" s="13" t="s">
+        <v>7899</v>
+      </c>
+      <c r="U798" s="14"/>
+      <c r="V798" s="14"/>
+      <c r="W798" s="14"/>
+      <c r="X798" s="14"/>
+      <c r="Y798" s="14"/>
+      <c r="Z798" s="13" t="s">
+        <v>7900</v>
+      </c>
+      <c r="AA798" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="799" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A799" s="13" t="s">
+        <v>7901</v>
+      </c>
+      <c r="B799" s="13" t="s">
+        <v>7902</v>
+      </c>
+      <c r="C799" s="13" t="s">
+        <v>6253</v>
+      </c>
+      <c r="D799" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E799" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F799" s="14"/>
+      <c r="G799" s="13" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H799" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="I799" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J799" s="13" t="s">
+        <v>4439</v>
+      </c>
+      <c r="K799" s="14"/>
+      <c r="L799" s="14"/>
+      <c r="M799" s="14"/>
+      <c r="N799" s="14"/>
+      <c r="O799" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P799" s="13" t="s">
+        <v>7903</v>
+      </c>
+      <c r="Q799" s="14"/>
+      <c r="R799" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S799" s="13" t="s">
+        <v>6074</v>
+      </c>
+      <c r="T799" s="14"/>
+      <c r="U799" s="14"/>
+      <c r="V799" s="14"/>
+      <c r="W799" s="14"/>
+      <c r="X799" s="14"/>
+      <c r="Y799" s="14"/>
+      <c r="Z799" s="14"/>
+      <c r="AA799" s="14"/>
+    </row>
+    <row r="800" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A800" s="13" t="s">
+        <v>7904</v>
+      </c>
+      <c r="B800" s="13" t="s">
+        <v>7905</v>
+      </c>
+      <c r="C800" s="13" t="s">
+        <v>5996</v>
+      </c>
+      <c r="D800" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E800" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F800" s="14"/>
+      <c r="G800" s="13" t="s">
+        <v>7906</v>
+      </c>
+      <c r="H800" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="I800" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J800" s="14"/>
+      <c r="K800" s="14"/>
+      <c r="L800" s="14"/>
+      <c r="M800" s="14"/>
+      <c r="N800" s="14"/>
+      <c r="O800" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="P800" s="13" t="s">
+        <v>7907</v>
+      </c>
+      <c r="Q800" s="14"/>
+      <c r="R800" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S800" s="14"/>
+      <c r="T800" s="13" t="s">
+        <v>7908</v>
+      </c>
+      <c r="U800" s="14"/>
+      <c r="V800" s="14"/>
+      <c r="W800" s="13" t="s">
+        <v>7909</v>
+      </c>
+      <c r="X800" s="14"/>
+      <c r="Y800" s="14"/>
+      <c r="Z800" s="13" t="s">
+        <v>7910</v>
+      </c>
+      <c r="AA800" s="14">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="801" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A801" s="13" t="s">
+        <v>7911</v>
+      </c>
+      <c r="B801" s="13" t="s">
+        <v>7912</v>
+      </c>
+      <c r="C801" s="13" t="s">
+        <v>7912</v>
+      </c>
+      <c r="D801" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E801" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F801" s="14"/>
+      <c r="G801" s="13" t="s">
+        <v>6358</v>
+      </c>
+      <c r="H801" s="13" t="s">
+        <v>3294</v>
+      </c>
+      <c r="I801" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J801" s="13" t="s">
+        <v>7913</v>
+      </c>
+      <c r="K801" s="14"/>
+      <c r="L801" s="14"/>
+      <c r="M801" s="14"/>
+      <c r="N801" s="14"/>
+      <c r="O801" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P801" s="13" t="s">
+        <v>7800</v>
+      </c>
+      <c r="Q801" s="14"/>
+      <c r="R801" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S801" s="13" t="s">
+        <v>5432</v>
+      </c>
+      <c r="T801" s="14"/>
+      <c r="U801" s="14"/>
+      <c r="V801" s="14"/>
+      <c r="W801" s="14"/>
+      <c r="X801" s="14"/>
+      <c r="Y801" s="14"/>
+      <c r="Z801" s="14"/>
+      <c r="AA801" s="14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="802" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A802" s="13" t="s">
+        <v>7914</v>
+      </c>
+      <c r="B802" s="13" t="s">
+        <v>7915</v>
+      </c>
+      <c r="C802" s="13" t="s">
+        <v>7916</v>
+      </c>
+      <c r="D802" s="14">
+        <v>2011</v>
+      </c>
+      <c r="E802" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F802" s="14"/>
+      <c r="G802" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H802" s="13" t="s">
+        <v>7917</v>
+      </c>
+      <c r="I802" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J802" s="13" t="s">
+        <v>7918</v>
+      </c>
+      <c r="K802" s="14"/>
+      <c r="L802" s="14"/>
+      <c r="M802" s="14"/>
+      <c r="N802" s="14"/>
+      <c r="O802" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P802" s="13" t="s">
+        <v>7919</v>
+      </c>
+      <c r="Q802" s="14"/>
+      <c r="R802" s="13" t="s">
+        <v>5457</v>
+      </c>
+      <c r="S802" s="14"/>
+      <c r="T802" s="13" t="s">
+        <v>7920</v>
+      </c>
+      <c r="U802" s="14"/>
+      <c r="V802" s="14"/>
+      <c r="W802" s="13" t="s">
+        <v>7921</v>
+      </c>
+      <c r="X802" s="14"/>
+      <c r="Y802" s="14"/>
+      <c r="Z802" s="13" t="s">
+        <v>7922</v>
+      </c>
+      <c r="AA802" s="14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="803" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A803" s="13" t="s">
+        <v>7923</v>
+      </c>
+      <c r="B803" s="13" t="s">
+        <v>7924</v>
+      </c>
+      <c r="C803" s="13" t="s">
+        <v>6142</v>
+      </c>
+      <c r="D803" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E803" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F803" s="14"/>
+      <c r="G803" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H803" s="13" t="s">
+        <v>7925</v>
+      </c>
+      <c r="I803" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J803" s="14"/>
+      <c r="K803" s="14"/>
+      <c r="L803" s="14"/>
+      <c r="M803" s="14"/>
+      <c r="N803" s="14"/>
+      <c r="O803" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P803" s="13" t="s">
+        <v>7926</v>
+      </c>
+      <c r="Q803" s="14"/>
+      <c r="R803" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S803" s="13" t="s">
+        <v>7752</v>
+      </c>
+      <c r="T803" s="13" t="s">
+        <v>7927</v>
+      </c>
+      <c r="U803" s="14"/>
+      <c r="V803" s="14"/>
+      <c r="W803" s="14"/>
+      <c r="X803" s="14"/>
+      <c r="Y803" s="14"/>
+      <c r="Z803" s="13" t="s">
+        <v>7928</v>
+      </c>
+      <c r="AA803" s="14">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="804" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A804" s="13" t="s">
+        <v>7929</v>
+      </c>
+      <c r="B804" s="13" t="s">
+        <v>7930</v>
+      </c>
+      <c r="C804" s="13" t="s">
+        <v>7931</v>
+      </c>
+      <c r="D804" s="14">
+        <v>2019</v>
+      </c>
+      <c r="E804" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F804" s="14"/>
+      <c r="G804" s="13" t="s">
+        <v>7932</v>
+      </c>
+      <c r="H804" s="14"/>
+      <c r="I804" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J804" s="13" t="s">
+        <v>7933</v>
+      </c>
+      <c r="K804" s="14"/>
+      <c r="L804" s="14"/>
+      <c r="M804" s="14"/>
+      <c r="N804" s="14"/>
+      <c r="O804" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P804" s="13" t="s">
+        <v>7934</v>
+      </c>
+      <c r="Q804" s="14"/>
+      <c r="R804" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S804" s="14"/>
+      <c r="T804" s="13" t="s">
+        <v>7935</v>
+      </c>
+      <c r="U804" s="14"/>
+      <c r="V804" s="14"/>
+      <c r="W804" s="14"/>
+      <c r="X804" s="14"/>
+      <c r="Y804" s="14"/>
+      <c r="Z804" s="13" t="s">
+        <v>7936</v>
+      </c>
+      <c r="AA804" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="805" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A805" s="13" t="s">
+        <v>7937</v>
+      </c>
+      <c r="B805" s="13" t="s">
+        <v>7938</v>
+      </c>
+      <c r="C805" s="13" t="s">
+        <v>6080</v>
+      </c>
+      <c r="D805" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E805" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F805" s="14"/>
+      <c r="G805" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H805" s="13" t="s">
+        <v>6218</v>
+      </c>
+      <c r="I805" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J805" s="13" t="s">
+        <v>4439</v>
+      </c>
+      <c r="K805" s="14"/>
+      <c r="L805" s="14"/>
+      <c r="M805" s="14"/>
+      <c r="N805" s="14"/>
+      <c r="O805" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="P805" s="13" t="s">
+        <v>7939</v>
+      </c>
+      <c r="Q805" s="14"/>
+      <c r="R805" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S805" s="14"/>
+      <c r="T805" s="13" t="s">
+        <v>7940</v>
+      </c>
+      <c r="U805" s="14"/>
+      <c r="V805" s="14"/>
+      <c r="W805" s="14"/>
+      <c r="X805" s="14"/>
+      <c r="Y805" s="14"/>
+      <c r="Z805" s="13" t="s">
+        <v>7941</v>
+      </c>
+      <c r="AA805" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="806" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A806" s="13" t="s">
+        <v>7942</v>
+      </c>
+      <c r="B806" s="13" t="s">
+        <v>7943</v>
+      </c>
+      <c r="C806" s="13" t="s">
+        <v>7916</v>
+      </c>
+      <c r="D806" s="14">
+        <v>2013</v>
+      </c>
+      <c r="E806" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F806" s="14"/>
+      <c r="G806" s="13" t="s">
+        <v>533</v>
+      </c>
+      <c r="H806" s="14"/>
+      <c r="I806" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J806" s="14"/>
+      <c r="K806" s="14"/>
+      <c r="L806" s="14"/>
+      <c r="M806" s="14"/>
+      <c r="N806" s="14"/>
+      <c r="O806" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P806" s="13" t="s">
+        <v>7944</v>
+      </c>
+      <c r="Q806" s="14"/>
+      <c r="R806" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S806" s="13" t="s">
+        <v>6470</v>
+      </c>
+      <c r="T806" s="13" t="s">
+        <v>7945</v>
+      </c>
+      <c r="U806" s="14"/>
+      <c r="V806" s="14"/>
+      <c r="W806" s="14"/>
+      <c r="X806" s="14"/>
+      <c r="Y806" s="14"/>
+      <c r="Z806" s="13" t="s">
+        <v>7946</v>
+      </c>
+      <c r="AA806" s="14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="807" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A807" s="13" t="s">
+        <v>7947</v>
+      </c>
+      <c r="B807" s="13" t="s">
+        <v>7948</v>
+      </c>
+      <c r="C807" s="13" t="s">
+        <v>5921</v>
+      </c>
+      <c r="D807" s="14">
+        <v>2014</v>
+      </c>
+      <c r="E807" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F807" s="14"/>
+      <c r="G807" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H807" s="14"/>
+      <c r="I807" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J807" s="14"/>
+      <c r="K807" s="14"/>
+      <c r="L807" s="14"/>
+      <c r="M807" s="14"/>
+      <c r="N807" s="14"/>
+      <c r="O807" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P807" s="13" t="s">
+        <v>7949</v>
+      </c>
+      <c r="Q807" s="14"/>
+      <c r="R807" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S807" s="13" t="s">
+        <v>1520</v>
+      </c>
+      <c r="T807" s="14"/>
+      <c r="U807" s="14"/>
+      <c r="V807" s="14"/>
+      <c r="W807" s="14"/>
+      <c r="X807" s="14"/>
+      <c r="Y807" s="14"/>
+      <c r="Z807" s="14"/>
+      <c r="AA807" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="808" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A808" s="13" t="s">
+        <v>7950</v>
+      </c>
+      <c r="B808" s="13" t="s">
+        <v>7951</v>
+      </c>
+      <c r="C808" s="13" t="s">
+        <v>7952</v>
+      </c>
+      <c r="D808" s="14">
+        <v>2015</v>
+      </c>
+      <c r="E808" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F808" s="14"/>
+      <c r="G808" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H808" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I808" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J808" s="13" t="s">
+        <v>7953</v>
+      </c>
+      <c r="K808" s="14"/>
+      <c r="L808" s="14"/>
+      <c r="M808" s="14"/>
+      <c r="N808" s="14"/>
+      <c r="O808" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P808" s="13" t="s">
+        <v>6377</v>
+      </c>
+      <c r="Q808" s="14"/>
+      <c r="R808" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S808" s="14"/>
+      <c r="T808" s="13" t="s">
+        <v>7954</v>
+      </c>
+      <c r="U808" s="14"/>
+      <c r="V808" s="14"/>
+      <c r="W808" s="14"/>
+      <c r="X808" s="14"/>
+      <c r="Y808" s="14"/>
+      <c r="Z808" s="13" t="s">
+        <v>7955</v>
+      </c>
+      <c r="AA808" s="14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="809" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A809" s="13" t="s">
+        <v>7956</v>
+      </c>
+      <c r="B809" s="13" t="s">
+        <v>7957</v>
+      </c>
+      <c r="C809" s="13" t="s">
+        <v>7952</v>
+      </c>
+      <c r="D809" s="14">
+        <v>2016</v>
+      </c>
+      <c r="E809" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F809" s="14"/>
+      <c r="G809" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H809" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="I809" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J809" s="13" t="s">
+        <v>7958</v>
+      </c>
+      <c r="K809" s="14"/>
+      <c r="L809" s="14"/>
+      <c r="M809" s="14"/>
+      <c r="N809" s="14"/>
+      <c r="O809" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P809" s="13" t="s">
+        <v>6228</v>
+      </c>
+      <c r="Q809" s="14"/>
+      <c r="R809" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S809" s="14"/>
+      <c r="T809" s="14"/>
+      <c r="U809" s="14"/>
+      <c r="V809" s="14"/>
+      <c r="W809" s="14"/>
+      <c r="X809" s="14"/>
+      <c r="Y809" s="14"/>
+      <c r="Z809" s="13" t="s">
+        <v>7959</v>
+      </c>
+      <c r="AA809" s="14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="810" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A810" s="13" t="s">
+        <v>7960</v>
+      </c>
+      <c r="B810" s="13" t="s">
+        <v>7961</v>
+      </c>
+      <c r="C810" s="13" t="s">
+        <v>6318</v>
+      </c>
+      <c r="D810" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E810" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F810" s="14"/>
+      <c r="G810" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H810" s="13" t="s">
+        <v>7962</v>
+      </c>
+      <c r="I810" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J810" s="13" t="s">
+        <v>7963</v>
+      </c>
+      <c r="K810" s="14"/>
+      <c r="L810" s="14"/>
+      <c r="M810" s="14"/>
+      <c r="N810" s="14"/>
+      <c r="O810" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P810" s="13" t="s">
+        <v>7964</v>
+      </c>
+      <c r="Q810" s="14"/>
+      <c r="R810" s="14"/>
+      <c r="S810" s="14"/>
+      <c r="T810" s="14"/>
+      <c r="U810" s="13" t="s">
+        <v>7965</v>
+      </c>
+      <c r="V810" s="14"/>
+      <c r="W810" s="13" t="s">
+        <v>7966</v>
+      </c>
+      <c r="X810" s="14"/>
+      <c r="Y810" s="14"/>
+      <c r="Z810" s="13" t="s">
+        <v>7967</v>
+      </c>
+      <c r="AA810" s="14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="811" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A811" s="13" t="s">
+        <v>7968</v>
+      </c>
+      <c r="B811" s="13" t="s">
+        <v>7969</v>
+      </c>
+      <c r="C811" s="13" t="s">
+        <v>6226</v>
+      </c>
+      <c r="D811" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E811" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F811" s="14"/>
+      <c r="G811" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H811" s="14"/>
+      <c r="I811" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J811" s="14"/>
+      <c r="K811" s="14"/>
+      <c r="L811" s="14"/>
+      <c r="M811" s="14"/>
+      <c r="N811" s="14"/>
+      <c r="O811" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P811" s="13" t="s">
+        <v>7970</v>
+      </c>
+      <c r="Q811" s="14"/>
+      <c r="R811" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S811" s="14"/>
+      <c r="T811" s="14"/>
+      <c r="U811" s="14"/>
+      <c r="V811" s="14"/>
+      <c r="W811" s="14"/>
+      <c r="X811" s="14"/>
+      <c r="Y811" s="13" t="s">
+        <v>6230</v>
+      </c>
+      <c r="Z811" s="13" t="s">
+        <v>7971</v>
+      </c>
+      <c r="AA811" s="14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="812" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A812" s="13" t="s">
+        <v>7972</v>
+      </c>
+      <c r="B812" s="13" t="s">
+        <v>7973</v>
+      </c>
+      <c r="C812" s="13" t="s">
+        <v>7799</v>
+      </c>
+      <c r="D812" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E812" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F812" s="14"/>
+      <c r="G812" s="13" t="s">
+        <v>2653</v>
+      </c>
+      <c r="H812" s="14"/>
+      <c r="I812" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J812" s="14"/>
+      <c r="K812" s="14"/>
+      <c r="L812" s="14"/>
+      <c r="M812" s="14"/>
+      <c r="N812" s="14"/>
+      <c r="O812" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="P812" s="13" t="s">
+        <v>7974</v>
+      </c>
+      <c r="Q812" s="14"/>
+      <c r="R812" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S812" s="13" t="s">
+        <v>7801</v>
+      </c>
+      <c r="T812" s="13" t="s">
+        <v>7975</v>
+      </c>
+      <c r="U812" s="14"/>
+      <c r="V812" s="14"/>
+      <c r="W812" s="14"/>
+      <c r="X812" s="14"/>
+      <c r="Y812" s="14"/>
+      <c r="Z812" s="13" t="s">
+        <v>7976</v>
+      </c>
+      <c r="AA812" s="14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="813" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A813" s="13" t="s">
+        <v>7977</v>
+      </c>
+      <c r="B813" s="13" t="s">
+        <v>7978</v>
+      </c>
+      <c r="C813" s="13" t="s">
+        <v>7979</v>
+      </c>
+      <c r="D813" s="14">
+        <v>2017</v>
+      </c>
+      <c r="E813" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F813" s="14"/>
+      <c r="G813" s="13" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H813" s="13" t="s">
+        <v>7980</v>
+      </c>
+      <c r="I813" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J813" s="14"/>
+      <c r="K813" s="14"/>
+      <c r="L813" s="14"/>
+      <c r="M813" s="14"/>
+      <c r="N813" s="14"/>
+      <c r="O813" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="P813" s="13" t="s">
+        <v>7981</v>
+      </c>
+      <c r="Q813" s="14"/>
+      <c r="R813" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S813" s="14"/>
+      <c r="T813" s="13" t="s">
+        <v>7982</v>
+      </c>
+      <c r="U813" s="14"/>
+      <c r="V813" s="14"/>
+      <c r="W813" s="13" t="s">
+        <v>7983</v>
+      </c>
+      <c r="X813" s="14"/>
+      <c r="Y813" s="14"/>
+      <c r="Z813" s="13" t="s">
+        <v>7984</v>
+      </c>
+      <c r="AA813" s="14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="814" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A814" s="13" t="s">
+        <v>7985</v>
+      </c>
+      <c r="B814" s="13" t="s">
+        <v>7973</v>
+      </c>
+      <c r="C814" s="13" t="s">
+        <v>7745</v>
+      </c>
+      <c r="D814" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E814" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F814" s="14"/>
+      <c r="G814" s="13" t="s">
+        <v>4106</v>
+      </c>
+      <c r="H814" s="13" t="s">
+        <v>7932</v>
+      </c>
+      <c r="I814" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J814" s="14"/>
+      <c r="K814" s="14"/>
+      <c r="L814" s="14"/>
+      <c r="M814" s="14"/>
+      <c r="N814" s="14"/>
+      <c r="O814" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="P814" s="13" t="s">
+        <v>7986</v>
+      </c>
+      <c r="Q814" s="14"/>
+      <c r="R814" s="13" t="s">
+        <v>3690</v>
+      </c>
+      <c r="S814" s="13" t="s">
+        <v>5590</v>
+      </c>
+      <c r="T814" s="14"/>
+      <c r="U814" s="13" t="s">
+        <v>7987</v>
+      </c>
+      <c r="V814" s="14"/>
+      <c r="W814" s="14"/>
+      <c r="X814" s="14"/>
+      <c r="Y814" s="14"/>
+      <c r="Z814" s="13" t="s">
+        <v>7988</v>
+      </c>
+      <c r="AA814" s="14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="815" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A815" s="13" t="s">
+        <v>7989</v>
+      </c>
+      <c r="B815" s="13" t="s">
+        <v>7990</v>
+      </c>
+      <c r="C815" s="13" t="s">
+        <v>5492</v>
+      </c>
+      <c r="D815" s="14">
+        <v>2018</v>
+      </c>
+      <c r="E815" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F815" s="14"/>
+      <c r="G815" s="13" t="s">
+        <v>5477</v>
+      </c>
+      <c r="H815" s="13" t="s">
+        <v>7991</v>
+      </c>
+      <c r="I815" s="13" t="s">
+        <v>3688</v>
+      </c>
+      <c r="J815" s="14"/>
+      <c r="K815" s="14"/>
+      <c r="L815" s="14"/>
+      <c r="M815" s="14"/>
+      <c r="N815" s="14"/>
+      <c r="O815" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="P815" s="13" t="s">
+        <v>7879</v>
+      </c>
+      <c r="Q815" s="14"/>
+      <c r="R815" s="14"/>
+      <c r="S815" s="14"/>
+      <c r="T815" s="13" t="s">
+        <v>7992</v>
+      </c>
+      <c r="U815" s="14"/>
+      <c r="V815" s="14"/>
+      <c r="W815" s="14"/>
+      <c r="X815" s="14"/>
+      <c r="Y815" s="14"/>
+      <c r="Z815" s="13" t="s">
+        <v>7993</v>
+      </c>
+      <c r="AA815" s="14">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200"/>
